--- a/.github/tmp_results.xlsx
+++ b/.github/tmp_results.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Sean Elvidge\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E84A7ABC-8BE1-4D50-9F4A-EF9BFF7CDA0F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EBFA1C5B-5F5A-4B7F-B822-F4C31A19FF01}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="25695" yWindow="0" windowWidth="26010" windowHeight="20985" xr2:uid="{156B8CF3-2535-45A6-80D2-358CC30668D6}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{156B8CF3-2535-45A6-80D2-358CC30668D6}"/>
   </bookViews>
   <sheets>
     <sheet name="Scores" sheetId="1" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="340" uniqueCount="172">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="325" uniqueCount="167">
   <si>
     <t>AFC Bournemouth</t>
   </si>
@@ -522,37 +522,22 @@
     <t>2-3</t>
   </si>
   <si>
-    <t>1-3</t>
-  </si>
-  <si>
-    <t>1-4</t>
-  </si>
-  <si>
-    <t>4-0</t>
-  </si>
-  <si>
     <t>3-0</t>
   </si>
   <si>
-    <t>3-3</t>
-  </si>
-  <si>
     <t>2-0</t>
   </si>
   <si>
-    <t>3-2</t>
-  </si>
-  <si>
     <t>2-2</t>
   </si>
   <si>
     <t>1-2</t>
   </si>
   <si>
-    <t>0-4</t>
-  </si>
-  <si>
-    <t>1-5</t>
+    <t>2-4</t>
+  </si>
+  <si>
+    <t>0-2</t>
   </si>
 </sst>
 </file>
@@ -930,15 +915,15 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{944D37C4-CAD2-4526-8947-361FF9BC37B9}">
   <dimension ref="A1:F45"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="10.5703125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="18.85546875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="10.54296875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="18.81640625" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="23" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="8.7109375" style="3"/>
+    <col min="6" max="6" width="8.7265625" style="3"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>149</v>
       </c>
@@ -958,15 +943,15 @@
         <v>152</v>
       </c>
     </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A2" s="2">
-        <v>46270</v>
+        <v>46283</v>
       </c>
       <c r="B2" t="s">
-        <v>91</v>
+        <v>21</v>
       </c>
       <c r="C2" t="s">
-        <v>0</v>
+        <v>36</v>
       </c>
       <c r="D2">
         <f>VLOOKUP(B2,Teams!A:B,2,FALSE)</f>
@@ -977,40 +962,40 @@
         <v>1</v>
       </c>
       <c r="F2" s="3" t="s">
-        <v>168</v>
-      </c>
-    </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A3" s="2">
-        <v>46270</v>
+        <v>46283</v>
       </c>
       <c r="B3" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="C3" t="s">
-        <v>126</v>
+        <v>135</v>
       </c>
       <c r="D3">
         <f>VLOOKUP(B3,Teams!A:B,2,FALSE)</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E3">
         <f>VLOOKUP(C3,Teams!A:B,2,FALSE)</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>154</v>
-      </c>
-    </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A4" s="2">
-        <v>46270</v>
+        <v>46284</v>
       </c>
       <c r="B4" t="s">
-        <v>22</v>
+        <v>132</v>
       </c>
       <c r="C4" t="s">
-        <v>70</v>
+        <v>9</v>
       </c>
       <c r="D4">
         <f>VLOOKUP(B4,Teams!A:B,2,FALSE)</f>
@@ -1021,18 +1006,18 @@
         <v>1</v>
       </c>
       <c r="F4" s="3" t="s">
-        <v>154</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A5" s="2">
-        <v>46270</v>
+        <v>46284</v>
       </c>
       <c r="B5" t="s">
-        <v>55</v>
+        <v>22</v>
       </c>
       <c r="C5" t="s">
-        <v>44</v>
+        <v>7</v>
       </c>
       <c r="D5">
         <f>VLOOKUP(B5,Teams!A:B,2,FALSE)</f>
@@ -1043,18 +1028,18 @@
         <v>1</v>
       </c>
       <c r="F5" s="3" t="s">
-        <v>160</v>
-      </c>
-    </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A6" s="2">
-        <v>46270</v>
+        <v>46284</v>
       </c>
       <c r="B6" t="s">
-        <v>79</v>
+        <v>51</v>
       </c>
       <c r="C6" t="s">
-        <v>41</v>
+        <v>67</v>
       </c>
       <c r="D6">
         <f>VLOOKUP(B6,Teams!A:B,2,FALSE)</f>
@@ -1068,15 +1053,15 @@
         <v>155</v>
       </c>
     </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A7" s="2">
-        <v>46270</v>
+        <v>46284</v>
       </c>
       <c r="B7" t="s">
-        <v>96</v>
+        <v>91</v>
       </c>
       <c r="C7" t="s">
-        <v>132</v>
+        <v>66</v>
       </c>
       <c r="D7">
         <f>VLOOKUP(B7,Teams!A:B,2,FALSE)</f>
@@ -1087,18 +1072,18 @@
         <v>1</v>
       </c>
       <c r="F7" s="3" t="s">
-        <v>159</v>
-      </c>
-    </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A8" s="2">
-        <v>46270</v>
+        <v>46284</v>
       </c>
       <c r="B8" t="s">
-        <v>66</v>
+        <v>96</v>
       </c>
       <c r="C8" t="s">
-        <v>9</v>
+        <v>41</v>
       </c>
       <c r="D8">
         <f>VLOOKUP(B8,Teams!A:B,2,FALSE)</f>
@@ -1109,18 +1094,18 @@
         <v>1</v>
       </c>
       <c r="F8" s="3" t="s">
-        <v>159</v>
-      </c>
-    </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A9" s="2">
-        <v>46270</v>
+        <v>46284</v>
       </c>
       <c r="B9" t="s">
-        <v>73</v>
+        <v>33</v>
       </c>
       <c r="C9" t="s">
-        <v>119</v>
+        <v>35</v>
       </c>
       <c r="D9">
         <f>VLOOKUP(B9,Teams!A:B,2,FALSE)</f>
@@ -1131,18 +1116,18 @@
         <v>2</v>
       </c>
       <c r="F9" s="3" t="s">
-        <v>154</v>
-      </c>
-    </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A10" s="2">
-        <v>46270</v>
+        <v>46284</v>
       </c>
       <c r="B10" t="s">
-        <v>104</v>
+        <v>85</v>
       </c>
       <c r="C10" t="s">
-        <v>14</v>
+        <v>137</v>
       </c>
       <c r="D10">
         <f>VLOOKUP(B10,Teams!A:B,2,FALSE)</f>
@@ -1153,18 +1138,18 @@
         <v>2</v>
       </c>
       <c r="F10" s="3" t="s">
-        <v>157</v>
-      </c>
-    </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A11" s="2">
-        <v>46270</v>
+        <v>46284</v>
       </c>
       <c r="B11" t="s">
         <v>125</v>
       </c>
       <c r="C11" t="s">
-        <v>35</v>
+        <v>115</v>
       </c>
       <c r="D11">
         <f>VLOOKUP(B11,Teams!A:B,2,FALSE)</f>
@@ -1175,18 +1160,18 @@
         <v>2</v>
       </c>
       <c r="F11" s="3" t="s">
-        <v>163</v>
-      </c>
-    </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A12" s="2">
-        <v>46270</v>
+        <v>46284</v>
       </c>
       <c r="B12" t="s">
-        <v>26</v>
+        <v>13</v>
       </c>
       <c r="C12" t="s">
-        <v>23</v>
+        <v>83</v>
       </c>
       <c r="D12">
         <f>VLOOKUP(B12,Teams!A:B,2,FALSE)</f>
@@ -1197,18 +1182,18 @@
         <v>2</v>
       </c>
       <c r="F12" s="3" t="s">
-        <v>169</v>
-      </c>
-    </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A13" s="2">
-        <v>46270</v>
+        <v>46284</v>
       </c>
       <c r="B13" t="s">
-        <v>85</v>
+        <v>26</v>
       </c>
       <c r="C13" t="s">
-        <v>16</v>
+        <v>48</v>
       </c>
       <c r="D13">
         <f>VLOOKUP(B13,Teams!A:B,2,FALSE)</f>
@@ -1219,18 +1204,18 @@
         <v>2</v>
       </c>
       <c r="F13" s="3" t="s">
-        <v>163</v>
-      </c>
-    </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.25">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A14" s="2">
-        <v>46270</v>
+        <v>46284</v>
       </c>
       <c r="B14" t="s">
-        <v>103</v>
+        <v>73</v>
       </c>
       <c r="C14" t="s">
-        <v>33</v>
+        <v>128</v>
       </c>
       <c r="D14">
         <f>VLOOKUP(B14,Teams!A:B,2,FALSE)</f>
@@ -1241,18 +1226,18 @@
         <v>2</v>
       </c>
       <c r="F14" s="3" t="s">
-        <v>166</v>
-      </c>
-    </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.25">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A15" s="2">
-        <v>46270</v>
+        <v>46284</v>
       </c>
       <c r="B15" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="C15" t="s">
-        <v>83</v>
+        <v>14</v>
       </c>
       <c r="D15">
         <f>VLOOKUP(B15,Teams!A:B,2,FALSE)</f>
@@ -1263,18 +1248,18 @@
         <v>2</v>
       </c>
       <c r="F15" s="3" t="s">
-        <v>158</v>
-      </c>
-    </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.25">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A16" s="2">
-        <v>46270</v>
+        <v>46284</v>
       </c>
       <c r="B16" t="s">
-        <v>115</v>
+        <v>105</v>
       </c>
       <c r="C16" t="s">
-        <v>95</v>
+        <v>104</v>
       </c>
       <c r="D16">
         <f>VLOOKUP(B16,Teams!A:B,2,FALSE)</f>
@@ -1285,18 +1270,18 @@
         <v>2</v>
       </c>
       <c r="F16" s="3" t="s">
-        <v>161</v>
-      </c>
-    </row>
-    <row r="17" spans="1:6" x14ac:dyDescent="0.25">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="17" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A17" s="2">
-        <v>46270</v>
+        <v>46284</v>
       </c>
       <c r="B17" t="s">
-        <v>136</v>
+        <v>143</v>
       </c>
       <c r="C17" t="s">
-        <v>135</v>
+        <v>119</v>
       </c>
       <c r="D17">
         <f>VLOOKUP(B17,Teams!A:B,2,FALSE)</f>
@@ -1307,62 +1292,62 @@
         <v>2</v>
       </c>
       <c r="F17" s="3" t="s">
-        <v>155</v>
-      </c>
-    </row>
-    <row r="18" spans="1:6" x14ac:dyDescent="0.25">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="18" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A18" s="2">
-        <v>46270</v>
+        <v>46284</v>
       </c>
       <c r="B18" t="s">
-        <v>137</v>
+        <v>11</v>
       </c>
       <c r="C18" t="s">
-        <v>48</v>
+        <v>71</v>
       </c>
       <c r="D18">
         <f>VLOOKUP(B18,Teams!A:B,2,FALSE)</f>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E18">
         <f>VLOOKUP(C18,Teams!A:B,2,FALSE)</f>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F18" s="3" t="s">
-        <v>164</v>
-      </c>
-    </row>
-    <row r="19" spans="1:6" x14ac:dyDescent="0.25">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="19" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A19" s="2">
-        <v>46270</v>
+        <v>46284</v>
       </c>
       <c r="B19" t="s">
-        <v>128</v>
+        <v>27</v>
       </c>
       <c r="C19" t="s">
-        <v>143</v>
+        <v>81</v>
       </c>
       <c r="D19">
         <f>VLOOKUP(B19,Teams!A:B,2,FALSE)</f>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E19">
         <f>VLOOKUP(C19,Teams!A:B,2,FALSE)</f>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F19" s="3" t="s">
-        <v>159</v>
-      </c>
-    </row>
-    <row r="20" spans="1:6" x14ac:dyDescent="0.25">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="20" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A20" s="2">
-        <v>46270</v>
+        <v>46284</v>
       </c>
       <c r="B20" t="s">
-        <v>100</v>
+        <v>15</v>
       </c>
       <c r="C20" t="s">
-        <v>116</v>
+        <v>101</v>
       </c>
       <c r="D20">
         <f>VLOOKUP(B20,Teams!A:B,2,FALSE)</f>
@@ -1373,18 +1358,18 @@
         <v>3</v>
       </c>
       <c r="F20" s="3" t="s">
-        <v>169</v>
-      </c>
-    </row>
-    <row r="21" spans="1:6" x14ac:dyDescent="0.25">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="21" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A21" s="2">
-        <v>46270</v>
+        <v>46284</v>
       </c>
       <c r="B21" t="s">
-        <v>138</v>
+        <v>25</v>
       </c>
       <c r="C21" t="s">
-        <v>124</v>
+        <v>65</v>
       </c>
       <c r="D21">
         <f>VLOOKUP(B21,Teams!A:B,2,FALSE)</f>
@@ -1395,15 +1380,15 @@
         <v>3</v>
       </c>
       <c r="F21" s="3" t="s">
-        <v>170</v>
-      </c>
-    </row>
-    <row r="22" spans="1:6" x14ac:dyDescent="0.25">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="22" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A22" s="2">
-        <v>46270</v>
+        <v>46284</v>
       </c>
       <c r="B22" t="s">
-        <v>11</v>
+        <v>72</v>
       </c>
       <c r="C22" t="s">
         <v>123</v>
@@ -1417,18 +1402,18 @@
         <v>3</v>
       </c>
       <c r="F22" s="3" t="s">
-        <v>171</v>
-      </c>
-    </row>
-    <row r="23" spans="1:6" x14ac:dyDescent="0.25">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="23" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A23" s="2">
-        <v>46270</v>
+        <v>46284</v>
       </c>
       <c r="B23" t="s">
+        <v>76</v>
+      </c>
+      <c r="C23" t="s">
         <v>19</v>
-      </c>
-      <c r="C23" t="s">
-        <v>81</v>
       </c>
       <c r="D23">
         <f>VLOOKUP(B23,Teams!A:B,2,FALSE)</f>
@@ -1439,15 +1424,15 @@
         <v>3</v>
       </c>
       <c r="F23" s="3" t="s">
-        <v>155</v>
-      </c>
-    </row>
-    <row r="24" spans="1:6" x14ac:dyDescent="0.25">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="24" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A24" s="2">
-        <v>46270</v>
+        <v>46284</v>
       </c>
       <c r="B24" t="s">
-        <v>27</v>
+        <v>99</v>
       </c>
       <c r="C24" t="s">
         <v>32</v>
@@ -1461,18 +1446,18 @@
         <v>3</v>
       </c>
       <c r="F24" s="3" t="s">
-        <v>168</v>
-      </c>
-    </row>
-    <row r="25" spans="1:6" x14ac:dyDescent="0.25">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="25" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A25" s="2">
-        <v>46270</v>
+        <v>46284</v>
       </c>
       <c r="B25" t="s">
+        <v>100</v>
+      </c>
+      <c r="C25" t="s">
         <v>49</v>
-      </c>
-      <c r="C25" t="s">
-        <v>101</v>
       </c>
       <c r="D25">
         <f>VLOOKUP(B25,Teams!A:B,2,FALSE)</f>
@@ -1483,15 +1468,15 @@
         <v>3</v>
       </c>
       <c r="F25" s="3" t="s">
-        <v>160</v>
-      </c>
-    </row>
-    <row r="26" spans="1:6" x14ac:dyDescent="0.25">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="26" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A26" s="2">
-        <v>46270</v>
+        <v>46284</v>
       </c>
       <c r="B26" t="s">
-        <v>65</v>
+        <v>106</v>
       </c>
       <c r="C26" t="s">
         <v>97</v>
@@ -1505,18 +1490,18 @@
         <v>3</v>
       </c>
       <c r="F26" s="3" t="s">
-        <v>154</v>
-      </c>
-    </row>
-    <row r="27" spans="1:6" x14ac:dyDescent="0.25">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="27" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A27" s="2">
-        <v>46270</v>
+        <v>46284</v>
       </c>
       <c r="B27" t="s">
-        <v>71</v>
+        <v>116</v>
       </c>
       <c r="C27" t="s">
-        <v>99</v>
+        <v>124</v>
       </c>
       <c r="D27">
         <f>VLOOKUP(B27,Teams!A:B,2,FALSE)</f>
@@ -1527,18 +1512,18 @@
         <v>3</v>
       </c>
       <c r="F27" s="3" t="s">
-        <v>170</v>
-      </c>
-    </row>
-    <row r="28" spans="1:6" x14ac:dyDescent="0.25">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="28" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A28" s="2">
-        <v>46270</v>
+        <v>46284</v>
       </c>
       <c r="B28" t="s">
-        <v>76</v>
+        <v>138</v>
       </c>
       <c r="C28" t="s">
-        <v>72</v>
+        <v>144</v>
       </c>
       <c r="D28">
         <f>VLOOKUP(B28,Teams!A:B,2,FALSE)</f>
@@ -1549,62 +1534,62 @@
         <v>3</v>
       </c>
       <c r="F28" s="3" t="s">
-        <v>154</v>
-      </c>
-    </row>
-    <row r="29" spans="1:6" x14ac:dyDescent="0.25">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="29" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A29" s="2">
-        <v>46270</v>
+        <v>46284</v>
       </c>
       <c r="B29" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="C29" t="s">
-        <v>15</v>
+        <v>98</v>
       </c>
       <c r="D29">
         <f>VLOOKUP(B29,Teams!A:B,2,FALSE)</f>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E29">
         <f>VLOOKUP(C29,Teams!A:B,2,FALSE)</f>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F29" s="3" t="s">
-        <v>156</v>
-      </c>
-    </row>
-    <row r="30" spans="1:6" x14ac:dyDescent="0.25">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="30" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A30" s="2">
-        <v>46270</v>
+        <v>46284</v>
       </c>
       <c r="B30" t="s">
-        <v>144</v>
+        <v>134</v>
       </c>
       <c r="C30" t="s">
-        <v>86</v>
+        <v>102</v>
       </c>
       <c r="D30">
         <f>VLOOKUP(B30,Teams!A:B,2,FALSE)</f>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E30">
         <f>VLOOKUP(C30,Teams!A:B,2,FALSE)</f>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F30" s="3" t="s">
-        <v>165</v>
-      </c>
-    </row>
-    <row r="31" spans="1:6" x14ac:dyDescent="0.25">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="31" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A31" s="2">
-        <v>46270</v>
+        <v>46284</v>
       </c>
       <c r="B31" t="s">
-        <v>53</v>
+        <v>4</v>
       </c>
       <c r="C31" t="s">
-        <v>117</v>
+        <v>92</v>
       </c>
       <c r="D31">
         <f>VLOOKUP(B31,Teams!A:B,2,FALSE)</f>
@@ -1615,18 +1600,18 @@
         <v>4</v>
       </c>
       <c r="F31" s="3" t="s">
-        <v>166</v>
-      </c>
-    </row>
-    <row r="32" spans="1:6" x14ac:dyDescent="0.25">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="32" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A32" s="2">
-        <v>46270</v>
+        <v>46284</v>
       </c>
       <c r="B32" t="s">
-        <v>112</v>
+        <v>10</v>
       </c>
       <c r="C32" t="s">
-        <v>102</v>
+        <v>53</v>
       </c>
       <c r="D32">
         <f>VLOOKUP(B32,Teams!A:B,2,FALSE)</f>
@@ -1637,18 +1622,18 @@
         <v>4</v>
       </c>
       <c r="F32" s="3" t="s">
-        <v>155</v>
-      </c>
-    </row>
-    <row r="33" spans="1:6" x14ac:dyDescent="0.25">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="33" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A33" s="2">
-        <v>46270</v>
+        <v>46284</v>
       </c>
       <c r="B33" t="s">
-        <v>4</v>
+        <v>37</v>
       </c>
       <c r="C33" t="s">
-        <v>42</v>
+        <v>146</v>
       </c>
       <c r="D33">
         <f>VLOOKUP(B33,Teams!A:B,2,FALSE)</f>
@@ -1659,18 +1644,18 @@
         <v>4</v>
       </c>
       <c r="F33" s="3" t="s">
-        <v>167</v>
-      </c>
-    </row>
-    <row r="34" spans="1:6" x14ac:dyDescent="0.25">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="34" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A34" s="2">
-        <v>46270</v>
+        <v>46284</v>
       </c>
       <c r="B34" t="s">
-        <v>24</v>
+        <v>40</v>
       </c>
       <c r="C34" t="s">
-        <v>110</v>
+        <v>37</v>
       </c>
       <c r="D34">
         <f>VLOOKUP(B34,Teams!A:B,2,FALSE)</f>
@@ -1681,18 +1666,18 @@
         <v>4</v>
       </c>
       <c r="F34" s="3" t="s">
-        <v>155</v>
-      </c>
-    </row>
-    <row r="35" spans="1:6" x14ac:dyDescent="0.25">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="35" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A35" s="2">
-        <v>46270</v>
+        <v>46284</v>
       </c>
       <c r="B35" t="s">
-        <v>37</v>
+        <v>43</v>
       </c>
       <c r="C35" t="s">
-        <v>60</v>
+        <v>117</v>
       </c>
       <c r="D35">
         <f>VLOOKUP(B35,Teams!A:B,2,FALSE)</f>
@@ -1703,18 +1688,18 @@
         <v>4</v>
       </c>
       <c r="F35" s="3" t="s">
-        <v>168</v>
-      </c>
-    </row>
-    <row r="36" spans="1:6" x14ac:dyDescent="0.25">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="36" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A36" s="2">
-        <v>46270</v>
+        <v>46284</v>
       </c>
       <c r="B36" t="s">
-        <v>39</v>
+        <v>52</v>
       </c>
       <c r="C36" t="s">
-        <v>10</v>
+        <v>133</v>
       </c>
       <c r="D36">
         <f>VLOOKUP(B36,Teams!A:B,2,FALSE)</f>
@@ -1725,18 +1710,18 @@
         <v>4</v>
       </c>
       <c r="F36" s="3" t="s">
-        <v>165</v>
-      </c>
-    </row>
-    <row r="37" spans="1:6" x14ac:dyDescent="0.25">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="37" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A37" s="2">
-        <v>46270</v>
+        <v>46284</v>
       </c>
       <c r="B37" t="s">
-        <v>43</v>
+        <v>58</v>
       </c>
       <c r="C37" t="s">
-        <v>146</v>
+        <v>24</v>
       </c>
       <c r="D37">
         <f>VLOOKUP(B37,Teams!A:B,2,FALSE)</f>
@@ -1747,18 +1732,18 @@
         <v>4</v>
       </c>
       <c r="F37" s="3" t="s">
-        <v>154</v>
-      </c>
-    </row>
-    <row r="38" spans="1:6" x14ac:dyDescent="0.25">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="38" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A38" s="2">
-        <v>46270</v>
+        <v>46284</v>
       </c>
       <c r="B38" t="s">
-        <v>52</v>
+        <v>60</v>
       </c>
       <c r="C38" t="s">
-        <v>134</v>
+        <v>42</v>
       </c>
       <c r="D38">
         <f>VLOOKUP(B38,Teams!A:B,2,FALSE)</f>
@@ -1769,18 +1754,18 @@
         <v>4</v>
       </c>
       <c r="F38" s="3" t="s">
-        <v>159</v>
-      </c>
-    </row>
-    <row r="39" spans="1:6" x14ac:dyDescent="0.25">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="39" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A39" s="2">
-        <v>46270</v>
+        <v>46284</v>
       </c>
       <c r="B39" t="s">
         <v>93</v>
       </c>
       <c r="C39" t="s">
-        <v>92</v>
+        <v>110</v>
       </c>
       <c r="D39">
         <f>VLOOKUP(B39,Teams!A:B,2,FALSE)</f>
@@ -1791,18 +1776,18 @@
         <v>4</v>
       </c>
       <c r="F39" s="3" t="s">
-        <v>155</v>
-      </c>
-    </row>
-    <row r="40" spans="1:6" x14ac:dyDescent="0.25">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="40" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A40" s="2">
-        <v>46270</v>
+        <v>46284</v>
       </c>
       <c r="B40" t="s">
-        <v>107</v>
+        <v>112</v>
       </c>
       <c r="C40" t="s">
-        <v>58</v>
+        <v>129</v>
       </c>
       <c r="D40">
         <f>VLOOKUP(B40,Teams!A:B,2,FALSE)</f>
@@ -1813,118 +1798,23 @@
         <v>4</v>
       </c>
       <c r="F40" s="3" t="s">
-        <v>162</v>
-      </c>
-    </row>
-    <row r="41" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A41" s="2">
-        <v>46270</v>
-      </c>
-      <c r="B41" t="s">
-        <v>129</v>
-      </c>
-      <c r="C41" t="s">
-        <v>40</v>
-      </c>
-      <c r="D41">
-        <f>VLOOKUP(B41,Teams!A:B,2,FALSE)</f>
-        <v>4</v>
-      </c>
-      <c r="E41">
-        <f>VLOOKUP(C41,Teams!A:B,2,FALSE)</f>
-        <v>4</v>
-      </c>
-      <c r="F41" s="3" t="s">
-        <v>156</v>
-      </c>
-    </row>
-    <row r="42" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A42" s="2">
-        <v>46270</v>
-      </c>
-      <c r="B42" t="s">
-        <v>133</v>
-      </c>
-      <c r="C42" t="s">
-        <v>98</v>
-      </c>
-      <c r="D42">
-        <f>VLOOKUP(B42,Teams!A:B,2,FALSE)</f>
-        <v>4</v>
-      </c>
-      <c r="E42">
-        <f>VLOOKUP(C42,Teams!A:B,2,FALSE)</f>
-        <v>4</v>
-      </c>
-      <c r="F42" s="3" t="s">
-        <v>166</v>
-      </c>
-    </row>
-    <row r="43" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A43" s="2">
-        <v>46271</v>
-      </c>
-      <c r="B43" t="s">
-        <v>51</v>
-      </c>
-      <c r="C43" t="s">
-        <v>80</v>
-      </c>
-      <c r="D43">
-        <f>VLOOKUP(B43,Teams!A:B,2,FALSE)</f>
-        <v>1</v>
-      </c>
-      <c r="E43">
-        <f>VLOOKUP(C43,Teams!A:B,2,FALSE)</f>
-        <v>1</v>
-      </c>
-      <c r="F43" s="3" t="s">
-        <v>168</v>
-      </c>
-    </row>
-    <row r="44" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A44" s="2">
-        <v>46271</v>
-      </c>
-      <c r="B44" t="s">
-        <v>7</v>
-      </c>
-      <c r="C44" t="s">
-        <v>36</v>
-      </c>
-      <c r="D44">
-        <f>VLOOKUP(B44,Teams!A:B,2,FALSE)</f>
-        <v>1</v>
-      </c>
-      <c r="E44">
-        <f>VLOOKUP(C44,Teams!A:B,2,FALSE)</f>
-        <v>1</v>
-      </c>
-      <c r="F44" s="3" t="s">
-        <v>157</v>
-      </c>
-    </row>
-    <row r="45" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A45" s="2">
-        <v>46271</v>
-      </c>
-      <c r="B45" t="s">
-        <v>13</v>
-      </c>
-      <c r="C45" t="s">
-        <v>141</v>
-      </c>
-      <c r="D45">
-        <f>VLOOKUP(B45,Teams!A:B,2,FALSE)</f>
-        <v>2</v>
-      </c>
-      <c r="E45">
-        <f>VLOOKUP(C45,Teams!A:B,2,FALSE)</f>
-        <v>2</v>
-      </c>
-      <c r="F45" s="3" t="s">
-        <v>168</v>
-      </c>
+        <v>155</v>
+      </c>
+    </row>
+    <row r="41" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A41" s="2"/>
+    </row>
+    <row r="42" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A42" s="2"/>
+    </row>
+    <row r="43" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A43" s="2"/>
+    </row>
+    <row r="44" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A44" s="2"/>
+    </row>
+    <row r="45" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A45" s="2"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -1946,13 +1836,13 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{660D5CBD-EF61-4F28-8F5F-C3B953B1D14A}">
   <dimension ref="A1:B147"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="23" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="8.7109375" style="1"/>
+    <col min="2" max="2" width="8.7265625" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1960,7 +1850,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>1</v>
       </c>
@@ -1968,7 +1858,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>2</v>
       </c>
@@ -1976,7 +1866,7 @@
         <v>148</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>3</v>
       </c>
@@ -1984,7 +1874,7 @@
         <v>148</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
         <v>4</v>
       </c>
@@ -1992,7 +1882,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
         <v>5</v>
       </c>
@@ -2000,7 +1890,7 @@
         <v>148</v>
       </c>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
         <v>6</v>
       </c>
@@ -2008,7 +1898,7 @@
         <v>148</v>
       </c>
     </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
         <v>7</v>
       </c>
@@ -2016,7 +1906,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
         <v>8</v>
       </c>
@@ -2024,7 +1914,7 @@
         <v>148</v>
       </c>
     </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
         <v>9</v>
       </c>
@@ -2032,7 +1922,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
         <v>10</v>
       </c>
@@ -2040,7 +1930,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A12" t="s">
         <v>11</v>
       </c>
@@ -2048,7 +1938,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A13" t="s">
         <v>12</v>
       </c>
@@ -2056,7 +1946,7 @@
         <v>148</v>
       </c>
     </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A14" t="s">
         <v>13</v>
       </c>
@@ -2064,7 +1954,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A15" t="s">
         <v>14</v>
       </c>
@@ -2072,7 +1962,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="16" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A16" t="s">
         <v>15</v>
       </c>
@@ -2080,7 +1970,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A17" t="s">
         <v>16</v>
       </c>
@@ -2088,7 +1978,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A18" t="s">
         <v>17</v>
       </c>
@@ -2096,7 +1986,7 @@
         <v>148</v>
       </c>
     </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A19" t="s">
         <v>18</v>
       </c>
@@ -2104,7 +1994,7 @@
         <v>148</v>
       </c>
     </row>
-    <row r="20" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A20" t="s">
         <v>19</v>
       </c>
@@ -2112,7 +2002,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="21" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A21" t="s">
         <v>20</v>
       </c>
@@ -2120,7 +2010,7 @@
         <v>148</v>
       </c>
     </row>
-    <row r="22" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A22" t="s">
         <v>21</v>
       </c>
@@ -2128,7 +2018,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="23" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A23" t="s">
         <v>22</v>
       </c>
@@ -2136,7 +2026,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="24" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A24" t="s">
         <v>23</v>
       </c>
@@ -2144,7 +2034,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="25" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A25" t="s">
         <v>24</v>
       </c>
@@ -2152,7 +2042,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="26" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A26" t="s">
         <v>25</v>
       </c>
@@ -2160,7 +2050,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="27" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A27" t="s">
         <v>26</v>
       </c>
@@ -2168,7 +2058,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="28" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A28" t="s">
         <v>27</v>
       </c>
@@ -2176,7 +2066,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="29" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A29" t="s">
         <v>28</v>
       </c>
@@ -2184,7 +2074,7 @@
         <v>148</v>
       </c>
     </row>
-    <row r="30" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A30" t="s">
         <v>29</v>
       </c>
@@ -2192,7 +2082,7 @@
         <v>148</v>
       </c>
     </row>
-    <row r="31" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A31" t="s">
         <v>30</v>
       </c>
@@ -2200,7 +2090,7 @@
         <v>148</v>
       </c>
     </row>
-    <row r="32" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A32" t="s">
         <v>31</v>
       </c>
@@ -2208,7 +2098,7 @@
         <v>148</v>
       </c>
     </row>
-    <row r="33" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A33" t="s">
         <v>32</v>
       </c>
@@ -2216,7 +2106,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="34" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A34" t="s">
         <v>33</v>
       </c>
@@ -2224,7 +2114,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="35" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A35" t="s">
         <v>34</v>
       </c>
@@ -2232,7 +2122,7 @@
         <v>148</v>
       </c>
     </row>
-    <row r="36" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A36" t="s">
         <v>35</v>
       </c>
@@ -2240,7 +2130,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="37" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A37" t="s">
         <v>36</v>
       </c>
@@ -2248,7 +2138,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="38" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A38" t="s">
         <v>37</v>
       </c>
@@ -2256,7 +2146,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="39" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A39" t="s">
         <v>38</v>
       </c>
@@ -2264,7 +2154,7 @@
         <v>148</v>
       </c>
     </row>
-    <row r="40" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A40" t="s">
         <v>39</v>
       </c>
@@ -2272,7 +2162,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="41" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A41" t="s">
         <v>40</v>
       </c>
@@ -2280,7 +2170,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="42" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A42" t="s">
         <v>41</v>
       </c>
@@ -2288,7 +2178,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="43" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A43" t="s">
         <v>42</v>
       </c>
@@ -2296,7 +2186,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="44" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A44" t="s">
         <v>43</v>
       </c>
@@ -2304,7 +2194,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="45" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A45" t="s">
         <v>44</v>
       </c>
@@ -2312,7 +2202,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="46" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A46" t="s">
         <v>45</v>
       </c>
@@ -2320,7 +2210,7 @@
         <v>148</v>
       </c>
     </row>
-    <row r="47" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A47" t="s">
         <v>46</v>
       </c>
@@ -2328,7 +2218,7 @@
         <v>148</v>
       </c>
     </row>
-    <row r="48" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A48" t="s">
         <v>47</v>
       </c>
@@ -2336,7 +2226,7 @@
         <v>148</v>
       </c>
     </row>
-    <row r="49" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A49" t="s">
         <v>48</v>
       </c>
@@ -2344,7 +2234,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="50" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A50" t="s">
         <v>49</v>
       </c>
@@ -2352,7 +2242,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="51" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A51" t="s">
         <v>50</v>
       </c>
@@ -2360,7 +2250,7 @@
         <v>148</v>
       </c>
     </row>
-    <row r="52" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A52" t="s">
         <v>51</v>
       </c>
@@ -2368,7 +2258,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="53" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A53" t="s">
         <v>52</v>
       </c>
@@ -2376,7 +2266,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="54" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A54" t="s">
         <v>53</v>
       </c>
@@ -2384,7 +2274,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="55" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A55" t="s">
         <v>54</v>
       </c>
@@ -2392,7 +2282,7 @@
         <v>148</v>
       </c>
     </row>
-    <row r="56" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A56" t="s">
         <v>55</v>
       </c>
@@ -2400,7 +2290,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="57" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A57" t="s">
         <v>56</v>
       </c>
@@ -2408,7 +2298,7 @@
         <v>148</v>
       </c>
     </row>
-    <row r="58" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A58" t="s">
         <v>57</v>
       </c>
@@ -2416,7 +2306,7 @@
         <v>148</v>
       </c>
     </row>
-    <row r="59" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A59" t="s">
         <v>58</v>
       </c>
@@ -2424,7 +2314,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="60" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A60" t="s">
         <v>59</v>
       </c>
@@ -2432,7 +2322,7 @@
         <v>148</v>
       </c>
     </row>
-    <row r="61" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A61" t="s">
         <v>60</v>
       </c>
@@ -2440,7 +2330,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="62" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A62" t="s">
         <v>61</v>
       </c>
@@ -2448,7 +2338,7 @@
         <v>148</v>
       </c>
     </row>
-    <row r="63" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A63" t="s">
         <v>62</v>
       </c>
@@ -2456,7 +2346,7 @@
         <v>148</v>
       </c>
     </row>
-    <row r="64" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A64" t="s">
         <v>63</v>
       </c>
@@ -2464,7 +2354,7 @@
         <v>148</v>
       </c>
     </row>
-    <row r="65" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A65" t="s">
         <v>64</v>
       </c>
@@ -2472,7 +2362,7 @@
         <v>148</v>
       </c>
     </row>
-    <row r="66" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A66" t="s">
         <v>65</v>
       </c>
@@ -2480,7 +2370,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="67" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A67" t="s">
         <v>66</v>
       </c>
@@ -2488,7 +2378,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="68" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A68" t="s">
         <v>67</v>
       </c>
@@ -2496,7 +2386,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="69" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A69" t="s">
         <v>68</v>
       </c>
@@ -2504,7 +2394,7 @@
         <v>148</v>
       </c>
     </row>
-    <row r="70" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A70" t="s">
         <v>69</v>
       </c>
@@ -2512,7 +2402,7 @@
         <v>148</v>
       </c>
     </row>
-    <row r="71" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A71" t="s">
         <v>70</v>
       </c>
@@ -2520,7 +2410,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="72" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A72" t="s">
         <v>71</v>
       </c>
@@ -2528,7 +2418,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="73" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A73" t="s">
         <v>72</v>
       </c>
@@ -2536,7 +2426,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="74" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A74" t="s">
         <v>73</v>
       </c>
@@ -2544,7 +2434,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="75" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A75" t="s">
         <v>74</v>
       </c>
@@ -2552,7 +2442,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="76" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A76" t="s">
         <v>75</v>
       </c>
@@ -2560,7 +2450,7 @@
         <v>148</v>
       </c>
     </row>
-    <row r="77" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A77" t="s">
         <v>76</v>
       </c>
@@ -2568,7 +2458,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="78" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A78" t="s">
         <v>77</v>
       </c>
@@ -2576,7 +2466,7 @@
         <v>148</v>
       </c>
     </row>
-    <row r="79" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A79" t="s">
         <v>78</v>
       </c>
@@ -2584,7 +2474,7 @@
         <v>148</v>
       </c>
     </row>
-    <row r="80" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A80" t="s">
         <v>79</v>
       </c>
@@ -2592,7 +2482,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="81" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A81" t="s">
         <v>80</v>
       </c>
@@ -2600,7 +2490,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="82" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A82" t="s">
         <v>81</v>
       </c>
@@ -2608,7 +2498,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="83" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A83" t="s">
         <v>82</v>
       </c>
@@ -2616,7 +2506,7 @@
         <v>148</v>
       </c>
     </row>
-    <row r="84" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A84" t="s">
         <v>83</v>
       </c>
@@ -2624,7 +2514,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="85" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A85" t="s">
         <v>84</v>
       </c>
@@ -2632,7 +2522,7 @@
         <v>148</v>
       </c>
     </row>
-    <row r="86" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A86" t="s">
         <v>85</v>
       </c>
@@ -2640,7 +2530,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="87" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A87" t="s">
         <v>86</v>
       </c>
@@ -2648,7 +2538,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="88" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A88" t="s">
         <v>87</v>
       </c>
@@ -2656,7 +2546,7 @@
         <v>148</v>
       </c>
     </row>
-    <row r="89" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A89" t="s">
         <v>88</v>
       </c>
@@ -2664,7 +2554,7 @@
         <v>148</v>
       </c>
     </row>
-    <row r="90" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A90" t="s">
         <v>89</v>
       </c>
@@ -2672,7 +2562,7 @@
         <v>148</v>
       </c>
     </row>
-    <row r="91" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A91" t="s">
         <v>90</v>
       </c>
@@ -2680,7 +2570,7 @@
         <v>148</v>
       </c>
     </row>
-    <row r="92" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A92" t="s">
         <v>91</v>
       </c>
@@ -2688,7 +2578,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="93" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A93" t="s">
         <v>92</v>
       </c>
@@ -2696,7 +2586,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="94" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A94" t="s">
         <v>93</v>
       </c>
@@ -2704,7 +2594,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="95" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A95" t="s">
         <v>94</v>
       </c>
@@ -2712,7 +2602,7 @@
         <v>148</v>
       </c>
     </row>
-    <row r="96" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A96" t="s">
         <v>95</v>
       </c>
@@ -2720,7 +2610,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="97" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A97" t="s">
         <v>96</v>
       </c>
@@ -2728,7 +2618,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="98" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A98" t="s">
         <v>97</v>
       </c>
@@ -2736,7 +2626,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="99" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A99" t="s">
         <v>98</v>
       </c>
@@ -2744,7 +2634,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="100" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="100" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A100" t="s">
         <v>99</v>
       </c>
@@ -2752,7 +2642,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="101" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="101" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A101" t="s">
         <v>100</v>
       </c>
@@ -2760,7 +2650,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="102" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="102" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A102" t="s">
         <v>101</v>
       </c>
@@ -2768,7 +2658,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="103" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="103" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A103" t="s">
         <v>102</v>
       </c>
@@ -2776,7 +2666,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="104" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="104" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A104" t="s">
         <v>103</v>
       </c>
@@ -2784,7 +2674,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="105" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="105" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A105" t="s">
         <v>104</v>
       </c>
@@ -2792,7 +2682,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="106" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="106" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A106" t="s">
         <v>105</v>
       </c>
@@ -2800,7 +2690,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="107" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="107" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A107" t="s">
         <v>106</v>
       </c>
@@ -2808,7 +2698,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="108" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="108" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A108" t="s">
         <v>107</v>
       </c>
@@ -2816,7 +2706,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="109" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="109" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A109" t="s">
         <v>108</v>
       </c>
@@ -2824,7 +2714,7 @@
         <v>148</v>
       </c>
     </row>
-    <row r="110" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="110" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A110" t="s">
         <v>109</v>
       </c>
@@ -2832,7 +2722,7 @@
         <v>148</v>
       </c>
     </row>
-    <row r="111" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="111" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A111" t="s">
         <v>110</v>
       </c>
@@ -2840,7 +2730,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="112" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="112" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A112" t="s">
         <v>111</v>
       </c>
@@ -2848,7 +2738,7 @@
         <v>148</v>
       </c>
     </row>
-    <row r="113" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="113" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A113" t="s">
         <v>112</v>
       </c>
@@ -2856,7 +2746,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="114" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="114" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A114" t="s">
         <v>113</v>
       </c>
@@ -2864,7 +2754,7 @@
         <v>148</v>
       </c>
     </row>
-    <row r="115" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="115" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A115" t="s">
         <v>114</v>
       </c>
@@ -2872,7 +2762,7 @@
         <v>148</v>
       </c>
     </row>
-    <row r="116" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="116" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A116" t="s">
         <v>115</v>
       </c>
@@ -2880,7 +2770,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="117" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="117" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A117" t="s">
         <v>116</v>
       </c>
@@ -2888,7 +2778,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="118" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="118" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A118" t="s">
         <v>117</v>
       </c>
@@ -2896,7 +2786,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="119" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="119" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A119" t="s">
         <v>118</v>
       </c>
@@ -2904,7 +2794,7 @@
         <v>148</v>
       </c>
     </row>
-    <row r="120" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="120" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A120" t="s">
         <v>119</v>
       </c>
@@ -2912,7 +2802,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="121" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="121" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A121" t="s">
         <v>120</v>
       </c>
@@ -2920,7 +2810,7 @@
         <v>148</v>
       </c>
     </row>
-    <row r="122" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="122" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A122" t="s">
         <v>121</v>
       </c>
@@ -2928,7 +2818,7 @@
         <v>148</v>
       </c>
     </row>
-    <row r="123" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="123" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A123" t="s">
         <v>122</v>
       </c>
@@ -2936,7 +2826,7 @@
         <v>148</v>
       </c>
     </row>
-    <row r="124" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="124" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A124" t="s">
         <v>123</v>
       </c>
@@ -2944,7 +2834,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="125" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="125" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A125" t="s">
         <v>124</v>
       </c>
@@ -2952,7 +2842,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="126" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="126" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A126" t="s">
         <v>125</v>
       </c>
@@ -2960,7 +2850,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="127" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="127" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A127" t="s">
         <v>126</v>
       </c>
@@ -2968,7 +2858,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="128" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="128" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A128" t="s">
         <v>127</v>
       </c>
@@ -2976,7 +2866,7 @@
         <v>148</v>
       </c>
     </row>
-    <row r="129" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="129" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A129" t="s">
         <v>128</v>
       </c>
@@ -2984,7 +2874,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="130" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="130" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A130" t="s">
         <v>129</v>
       </c>
@@ -2992,7 +2882,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="131" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="131" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A131" t="s">
         <v>130</v>
       </c>
@@ -3000,7 +2890,7 @@
         <v>148</v>
       </c>
     </row>
-    <row r="132" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="132" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A132" t="s">
         <v>131</v>
       </c>
@@ -3008,7 +2898,7 @@
         <v>148</v>
       </c>
     </row>
-    <row r="133" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="133" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A133" t="s">
         <v>132</v>
       </c>
@@ -3016,7 +2906,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="134" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="134" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A134" t="s">
         <v>133</v>
       </c>
@@ -3024,7 +2914,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="135" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="135" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A135" t="s">
         <v>134</v>
       </c>
@@ -3032,7 +2922,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="136" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="136" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A136" t="s">
         <v>135</v>
       </c>
@@ -3040,7 +2930,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="137" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="137" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A137" t="s">
         <v>136</v>
       </c>
@@ -3048,7 +2938,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="138" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="138" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A138" t="s">
         <v>137</v>
       </c>
@@ -3056,7 +2946,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="139" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="139" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A139" t="s">
         <v>138</v>
       </c>
@@ -3064,7 +2954,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="140" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="140" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A140" t="s">
         <v>139</v>
       </c>
@@ -3072,7 +2962,7 @@
         <v>148</v>
       </c>
     </row>
-    <row r="141" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="141" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A141" t="s">
         <v>140</v>
       </c>
@@ -3080,7 +2970,7 @@
         <v>148</v>
       </c>
     </row>
-    <row r="142" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="142" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A142" t="s">
         <v>141</v>
       </c>
@@ -3088,7 +2978,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="143" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="143" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A143" t="s">
         <v>142</v>
       </c>
@@ -3096,7 +2986,7 @@
         <v>148</v>
       </c>
     </row>
-    <row r="144" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="144" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A144" t="s">
         <v>143</v>
       </c>
@@ -3104,7 +2994,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="145" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="145" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A145" t="s">
         <v>144</v>
       </c>
@@ -3112,7 +3002,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="146" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="146" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A146" t="s">
         <v>145</v>
       </c>
@@ -3120,7 +3010,7 @@
         <v>148</v>
       </c>
     </row>
-    <row r="147" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="147" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A147" t="s">
         <v>146</v>
       </c>

--- a/.github/tmp_results.xlsx
+++ b/.github/tmp_results.xlsx
@@ -1630,7 +1630,7 @@
         <v>46284</v>
       </c>
       <c r="B33" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="C33" t="s">
         <v>146</v>

--- a/.github/tmp_results.xlsx
+++ b/.github/tmp_results.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30430"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Sean Elvidge\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EBFA1C5B-5F5A-4B7F-B822-F4C31A19FF01}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6055D06B-3F36-4C70-B3D7-7A8027DCA24C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{156B8CF3-2535-45A6-80D2-358CC30668D6}"/>
+    <workbookView xWindow="9510" yWindow="0" windowWidth="9780" windowHeight="11370" xr2:uid="{156B8CF3-2535-45A6-80D2-358CC30668D6}"/>
   </bookViews>
   <sheets>
     <sheet name="Scores" sheetId="1" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="325" uniqueCount="167">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="322" uniqueCount="169">
   <si>
     <t>AFC Bournemouth</t>
   </si>
@@ -507,9 +507,6 @@
     <t>1-0</t>
   </si>
   <si>
-    <t>3-1</t>
-  </si>
-  <si>
     <t>2-1</t>
   </si>
   <si>
@@ -522,22 +519,31 @@
     <t>2-3</t>
   </si>
   <si>
-    <t>3-0</t>
-  </si>
-  <si>
     <t>2-0</t>
   </si>
   <si>
-    <t>2-2</t>
-  </si>
-  <si>
-    <t>1-2</t>
-  </si>
-  <si>
-    <t>2-4</t>
-  </si>
-  <si>
     <t>0-2</t>
+  </si>
+  <si>
+    <t>1-3</t>
+  </si>
+  <si>
+    <t>4-1</t>
+  </si>
+  <si>
+    <t>5-0</t>
+  </si>
+  <si>
+    <t>1-4</t>
+  </si>
+  <si>
+    <t>5-1</t>
+  </si>
+  <si>
+    <t>0-5</t>
+  </si>
+  <si>
+    <t>3-3</t>
   </si>
 </sst>
 </file>
@@ -945,13 +951,13 @@
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A2" s="2">
-        <v>46283</v>
+        <v>46319</v>
       </c>
       <c r="B2" t="s">
-        <v>21</v>
+        <v>9</v>
       </c>
       <c r="C2" t="s">
-        <v>36</v>
+        <v>79</v>
       </c>
       <c r="D2">
         <f>VLOOKUP(B2,Teams!A:B,2,FALSE)</f>
@@ -962,40 +968,40 @@
         <v>1</v>
       </c>
       <c r="F2" s="3" t="s">
-        <v>161</v>
+        <v>156</v>
       </c>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A3" s="2">
-        <v>46283</v>
+        <v>46319</v>
       </c>
       <c r="B3" t="s">
-        <v>23</v>
+        <v>7</v>
       </c>
       <c r="C3" t="s">
-        <v>135</v>
+        <v>51</v>
       </c>
       <c r="D3">
         <f>VLOOKUP(B3,Teams!A:B,2,FALSE)</f>
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E3">
         <f>VLOOKUP(C3,Teams!A:B,2,FALSE)</f>
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>155</v>
+        <v>160</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A4" s="2">
-        <v>46284</v>
+        <v>46319</v>
       </c>
       <c r="B4" t="s">
-        <v>132</v>
+        <v>41</v>
       </c>
       <c r="C4" t="s">
-        <v>9</v>
+        <v>55</v>
       </c>
       <c r="D4">
         <f>VLOOKUP(B4,Teams!A:B,2,FALSE)</f>
@@ -1006,18 +1012,18 @@
         <v>1</v>
       </c>
       <c r="F4" s="3" t="s">
-        <v>160</v>
+        <v>157</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A5" s="2">
-        <v>46284</v>
+        <v>46319</v>
       </c>
       <c r="B5" t="s">
-        <v>22</v>
+        <v>36</v>
       </c>
       <c r="C5" t="s">
-        <v>7</v>
+        <v>132</v>
       </c>
       <c r="D5">
         <f>VLOOKUP(B5,Teams!A:B,2,FALSE)</f>
@@ -1033,79 +1039,79 @@
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A6" s="2">
-        <v>46284</v>
+        <v>46319</v>
       </c>
       <c r="B6" t="s">
-        <v>51</v>
+        <v>35</v>
       </c>
       <c r="C6" t="s">
-        <v>67</v>
+        <v>95</v>
       </c>
       <c r="D6">
         <f>VLOOKUP(B6,Teams!A:B,2,FALSE)</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E6">
         <f>VLOOKUP(C6,Teams!A:B,2,FALSE)</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F6" s="3" t="s">
-        <v>155</v>
+        <v>162</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A7" s="2">
-        <v>46284</v>
+        <v>46319</v>
       </c>
       <c r="B7" t="s">
-        <v>91</v>
+        <v>103</v>
       </c>
       <c r="C7" t="s">
-        <v>66</v>
+        <v>85</v>
       </c>
       <c r="D7">
         <f>VLOOKUP(B7,Teams!A:B,2,FALSE)</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E7">
         <f>VLOOKUP(C7,Teams!A:B,2,FALSE)</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F7" s="3" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A8" s="2">
-        <v>46284</v>
+        <v>46319</v>
       </c>
       <c r="B8" t="s">
-        <v>96</v>
+        <v>115</v>
       </c>
       <c r="C8" t="s">
-        <v>41</v>
+        <v>48</v>
       </c>
       <c r="D8">
         <f>VLOOKUP(B8,Teams!A:B,2,FALSE)</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E8">
         <f>VLOOKUP(C8,Teams!A:B,2,FALSE)</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F8" s="3" t="s">
-        <v>158</v>
+        <v>154</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A9" s="2">
-        <v>46284</v>
+        <v>46319</v>
       </c>
       <c r="B9" t="s">
-        <v>33</v>
+        <v>14</v>
       </c>
       <c r="C9" t="s">
-        <v>35</v>
+        <v>143</v>
       </c>
       <c r="D9">
         <f>VLOOKUP(B9,Teams!A:B,2,FALSE)</f>
@@ -1116,18 +1122,18 @@
         <v>2</v>
       </c>
       <c r="F9" s="3" t="s">
-        <v>156</v>
+        <v>160</v>
       </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A10" s="2">
-        <v>46284</v>
+        <v>46319</v>
       </c>
       <c r="B10" t="s">
-        <v>85</v>
+        <v>33</v>
       </c>
       <c r="C10" t="s">
-        <v>137</v>
+        <v>13</v>
       </c>
       <c r="D10">
         <f>VLOOKUP(B10,Teams!A:B,2,FALSE)</f>
@@ -1138,18 +1144,18 @@
         <v>2</v>
       </c>
       <c r="F10" s="3" t="s">
-        <v>163</v>
+        <v>155</v>
       </c>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A11" s="2">
-        <v>46284</v>
+        <v>46319</v>
       </c>
       <c r="B11" t="s">
-        <v>125</v>
+        <v>73</v>
       </c>
       <c r="C11" t="s">
-        <v>115</v>
+        <v>26</v>
       </c>
       <c r="D11">
         <f>VLOOKUP(B11,Teams!A:B,2,FALSE)</f>
@@ -1160,18 +1166,18 @@
         <v>2</v>
       </c>
       <c r="F11" s="3" t="s">
-        <v>157</v>
+        <v>163</v>
       </c>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A12" s="2">
-        <v>46284</v>
+        <v>46319</v>
       </c>
       <c r="B12" t="s">
-        <v>13</v>
+        <v>104</v>
       </c>
       <c r="C12" t="s">
-        <v>83</v>
+        <v>136</v>
       </c>
       <c r="D12">
         <f>VLOOKUP(B12,Teams!A:B,2,FALSE)</f>
@@ -1182,18 +1188,18 @@
         <v>2</v>
       </c>
       <c r="F12" s="3" t="s">
-        <v>163</v>
+        <v>154</v>
       </c>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A13" s="2">
-        <v>46284</v>
+        <v>46319</v>
       </c>
       <c r="B13" t="s">
-        <v>26</v>
+        <v>105</v>
       </c>
       <c r="C13" t="s">
-        <v>48</v>
+        <v>128</v>
       </c>
       <c r="D13">
         <f>VLOOKUP(B13,Teams!A:B,2,FALSE)</f>
@@ -1204,18 +1210,18 @@
         <v>2</v>
       </c>
       <c r="F13" s="3" t="s">
-        <v>154</v>
+        <v>164</v>
       </c>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A14" s="2">
-        <v>46284</v>
+        <v>46319</v>
       </c>
       <c r="B14" t="s">
-        <v>73</v>
+        <v>125</v>
       </c>
       <c r="C14" t="s">
-        <v>128</v>
+        <v>23</v>
       </c>
       <c r="D14">
         <f>VLOOKUP(B14,Teams!A:B,2,FALSE)</f>
@@ -1226,18 +1232,18 @@
         <v>2</v>
       </c>
       <c r="F14" s="3" t="s">
-        <v>164</v>
+        <v>158</v>
       </c>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A15" s="2">
-        <v>46284</v>
+        <v>46319</v>
       </c>
       <c r="B15" t="s">
-        <v>103</v>
+        <v>137</v>
       </c>
       <c r="C15" t="s">
-        <v>14</v>
+        <v>119</v>
       </c>
       <c r="D15">
         <f>VLOOKUP(B15,Teams!A:B,2,FALSE)</f>
@@ -1248,18 +1254,18 @@
         <v>2</v>
       </c>
       <c r="F15" s="3" t="s">
-        <v>163</v>
+        <v>159</v>
       </c>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A16" s="2">
-        <v>46284</v>
+        <v>46319</v>
       </c>
       <c r="B16" t="s">
-        <v>105</v>
+        <v>141</v>
       </c>
       <c r="C16" t="s">
-        <v>104</v>
+        <v>135</v>
       </c>
       <c r="D16">
         <f>VLOOKUP(B16,Teams!A:B,2,FALSE)</f>
@@ -1270,37 +1276,37 @@
         <v>2</v>
       </c>
       <c r="F16" s="3" t="s">
-        <v>163</v>
+        <v>155</v>
       </c>
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A17" s="2">
-        <v>46284</v>
+        <v>46319</v>
       </c>
       <c r="B17" t="s">
-        <v>143</v>
+        <v>65</v>
       </c>
       <c r="C17" t="s">
-        <v>119</v>
+        <v>138</v>
       </c>
       <c r="D17">
         <f>VLOOKUP(B17,Teams!A:B,2,FALSE)</f>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E17">
         <f>VLOOKUP(C17,Teams!A:B,2,FALSE)</f>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F17" s="3" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A18" s="2">
-        <v>46284</v>
+        <v>46319</v>
       </c>
       <c r="B18" t="s">
-        <v>11</v>
+        <v>76</v>
       </c>
       <c r="C18" t="s">
         <v>71</v>
@@ -1314,18 +1320,18 @@
         <v>3</v>
       </c>
       <c r="F18" s="3" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A19" s="2">
-        <v>46284</v>
+        <v>46319</v>
       </c>
       <c r="B19" t="s">
-        <v>27</v>
+        <v>1</v>
       </c>
       <c r="C19" t="s">
-        <v>81</v>
+        <v>144</v>
       </c>
       <c r="D19">
         <f>VLOOKUP(B19,Teams!A:B,2,FALSE)</f>
@@ -1336,18 +1342,18 @@
         <v>3</v>
       </c>
       <c r="F19" s="3" t="s">
-        <v>163</v>
+        <v>154</v>
       </c>
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A20" s="2">
-        <v>46284</v>
+        <v>46319</v>
       </c>
       <c r="B20" t="s">
         <v>15</v>
       </c>
       <c r="C20" t="s">
-        <v>101</v>
+        <v>81</v>
       </c>
       <c r="D20">
         <f>VLOOKUP(B20,Teams!A:B,2,FALSE)</f>
@@ -1363,13 +1369,13 @@
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A21" s="2">
-        <v>46284</v>
+        <v>46319</v>
       </c>
       <c r="B21" t="s">
         <v>25</v>
       </c>
       <c r="C21" t="s">
-        <v>65</v>
+        <v>100</v>
       </c>
       <c r="D21">
         <f>VLOOKUP(B21,Teams!A:B,2,FALSE)</f>
@@ -1380,18 +1386,18 @@
         <v>3</v>
       </c>
       <c r="F21" s="3" t="s">
-        <v>157</v>
+        <v>154</v>
       </c>
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A22" s="2">
-        <v>46284</v>
+        <v>46319</v>
       </c>
       <c r="B22" t="s">
+        <v>27</v>
+      </c>
+      <c r="C22" t="s">
         <v>72</v>
-      </c>
-      <c r="C22" t="s">
-        <v>123</v>
       </c>
       <c r="D22">
         <f>VLOOKUP(B22,Teams!A:B,2,FALSE)</f>
@@ -1402,18 +1408,18 @@
         <v>3</v>
       </c>
       <c r="F22" s="3" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
     </row>
     <row r="23" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A23" s="2">
-        <v>46284</v>
+        <v>46319</v>
       </c>
       <c r="B23" t="s">
-        <v>76</v>
+        <v>32</v>
       </c>
       <c r="C23" t="s">
-        <v>19</v>
+        <v>101</v>
       </c>
       <c r="D23">
         <f>VLOOKUP(B23,Teams!A:B,2,FALSE)</f>
@@ -1424,18 +1430,18 @@
         <v>3</v>
       </c>
       <c r="F23" s="3" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
     </row>
     <row r="24" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A24" s="2">
-        <v>46284</v>
+        <v>46319</v>
       </c>
       <c r="B24" t="s">
-        <v>99</v>
+        <v>49</v>
       </c>
       <c r="C24" t="s">
-        <v>32</v>
+        <v>116</v>
       </c>
       <c r="D24">
         <f>VLOOKUP(B24,Teams!A:B,2,FALSE)</f>
@@ -1446,18 +1452,18 @@
         <v>3</v>
       </c>
       <c r="F24" s="3" t="s">
-        <v>154</v>
+        <v>160</v>
       </c>
     </row>
     <row r="25" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A25" s="2">
-        <v>46284</v>
+        <v>46319</v>
       </c>
       <c r="B25" t="s">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="C25" t="s">
-        <v>49</v>
+        <v>124</v>
       </c>
       <c r="D25">
         <f>VLOOKUP(B25,Teams!A:B,2,FALSE)</f>
@@ -1468,18 +1474,18 @@
         <v>3</v>
       </c>
       <c r="F25" s="3" t="s">
-        <v>166</v>
+        <v>154</v>
       </c>
     </row>
     <row r="26" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A26" s="2">
-        <v>46284</v>
+        <v>46319</v>
       </c>
       <c r="B26" t="s">
-        <v>106</v>
+        <v>99</v>
       </c>
       <c r="C26" t="s">
-        <v>97</v>
+        <v>19</v>
       </c>
       <c r="D26">
         <f>VLOOKUP(B26,Teams!A:B,2,FALSE)</f>
@@ -1490,18 +1496,18 @@
         <v>3</v>
       </c>
       <c r="F26" s="3" t="s">
-        <v>162</v>
+        <v>158</v>
       </c>
     </row>
     <row r="27" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A27" s="2">
-        <v>46284</v>
+        <v>46319</v>
       </c>
       <c r="B27" t="s">
-        <v>116</v>
+        <v>106</v>
       </c>
       <c r="C27" t="s">
-        <v>124</v>
+        <v>11</v>
       </c>
       <c r="D27">
         <f>VLOOKUP(B27,Teams!A:B,2,FALSE)</f>
@@ -1512,18 +1518,18 @@
         <v>3</v>
       </c>
       <c r="F27" s="3" t="s">
-        <v>159</v>
+        <v>156</v>
       </c>
     </row>
     <row r="28" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A28" s="2">
-        <v>46284</v>
+        <v>46319</v>
       </c>
       <c r="B28" t="s">
-        <v>138</v>
+        <v>123</v>
       </c>
       <c r="C28" t="s">
-        <v>144</v>
+        <v>86</v>
       </c>
       <c r="D28">
         <f>VLOOKUP(B28,Teams!A:B,2,FALSE)</f>
@@ -1534,18 +1540,18 @@
         <v>3</v>
       </c>
       <c r="F28" s="3" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
     </row>
     <row r="29" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A29" s="2">
-        <v>46284</v>
+        <v>46319</v>
       </c>
       <c r="B29" t="s">
-        <v>107</v>
+        <v>24</v>
       </c>
       <c r="C29" t="s">
-        <v>98</v>
+        <v>129</v>
       </c>
       <c r="D29">
         <f>VLOOKUP(B29,Teams!A:B,2,FALSE)</f>
@@ -1556,18 +1562,18 @@
         <v>4</v>
       </c>
       <c r="F29" s="3" t="s">
-        <v>162</v>
+        <v>158</v>
       </c>
     </row>
     <row r="30" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A30" s="2">
-        <v>46284</v>
+        <v>46319</v>
       </c>
       <c r="B30" t="s">
-        <v>134</v>
+        <v>37</v>
       </c>
       <c r="C30" t="s">
-        <v>102</v>
+        <v>92</v>
       </c>
       <c r="D30">
         <f>VLOOKUP(B30,Teams!A:B,2,FALSE)</f>
@@ -1578,18 +1584,18 @@
         <v>4</v>
       </c>
       <c r="F30" s="3" t="s">
-        <v>162</v>
+        <v>155</v>
       </c>
     </row>
     <row r="31" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A31" s="2">
-        <v>46284</v>
+        <v>46319</v>
       </c>
       <c r="B31" t="s">
-        <v>4</v>
+        <v>93</v>
       </c>
       <c r="C31" t="s">
-        <v>92</v>
+        <v>40</v>
       </c>
       <c r="D31">
         <f>VLOOKUP(B31,Teams!A:B,2,FALSE)</f>
@@ -1600,18 +1606,18 @@
         <v>4</v>
       </c>
       <c r="F31" s="3" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
     </row>
     <row r="32" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A32" s="2">
-        <v>46284</v>
+        <v>46319</v>
       </c>
       <c r="B32" t="s">
         <v>10</v>
       </c>
       <c r="C32" t="s">
-        <v>53</v>
+        <v>98</v>
       </c>
       <c r="D32">
         <f>VLOOKUP(B32,Teams!A:B,2,FALSE)</f>
@@ -1622,18 +1628,18 @@
         <v>4</v>
       </c>
       <c r="F32" s="3" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
     </row>
     <row r="33" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A33" s="2">
-        <v>46284</v>
+        <v>46319</v>
       </c>
       <c r="B33" t="s">
         <v>39</v>
       </c>
       <c r="C33" t="s">
-        <v>146</v>
+        <v>43</v>
       </c>
       <c r="D33">
         <f>VLOOKUP(B33,Teams!A:B,2,FALSE)</f>
@@ -1644,18 +1650,18 @@
         <v>4</v>
       </c>
       <c r="F33" s="3" t="s">
-        <v>162</v>
+        <v>166</v>
       </c>
     </row>
     <row r="34" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A34" s="2">
-        <v>46284</v>
+        <v>46319</v>
       </c>
       <c r="B34" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="C34" t="s">
-        <v>37</v>
+        <v>133</v>
       </c>
       <c r="D34">
         <f>VLOOKUP(B34,Teams!A:B,2,FALSE)</f>
@@ -1671,13 +1677,13 @@
     </row>
     <row r="35" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A35" s="2">
-        <v>46284</v>
+        <v>46319</v>
       </c>
       <c r="B35" t="s">
-        <v>43</v>
+        <v>52</v>
       </c>
       <c r="C35" t="s">
-        <v>117</v>
+        <v>53</v>
       </c>
       <c r="D35">
         <f>VLOOKUP(B35,Teams!A:B,2,FALSE)</f>
@@ -1688,18 +1694,18 @@
         <v>4</v>
       </c>
       <c r="F35" s="3" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
     </row>
     <row r="36" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A36" s="2">
-        <v>46284</v>
+        <v>46319</v>
       </c>
       <c r="B36" t="s">
-        <v>52</v>
+        <v>58</v>
       </c>
       <c r="C36" t="s">
-        <v>133</v>
+        <v>60</v>
       </c>
       <c r="D36">
         <f>VLOOKUP(B36,Teams!A:B,2,FALSE)</f>
@@ -1710,18 +1716,18 @@
         <v>4</v>
       </c>
       <c r="F36" s="3" t="s">
-        <v>159</v>
+        <v>165</v>
       </c>
     </row>
     <row r="37" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A37" s="2">
-        <v>46284</v>
+        <v>46319</v>
       </c>
       <c r="B37" t="s">
-        <v>58</v>
+        <v>107</v>
       </c>
       <c r="C37" t="s">
-        <v>24</v>
+        <v>4</v>
       </c>
       <c r="D37">
         <f>VLOOKUP(B37,Teams!A:B,2,FALSE)</f>
@@ -1732,18 +1738,18 @@
         <v>4</v>
       </c>
       <c r="F37" s="3" t="s">
-        <v>161</v>
+        <v>167</v>
       </c>
     </row>
     <row r="38" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A38" s="2">
-        <v>46284</v>
+        <v>46319</v>
       </c>
       <c r="B38" t="s">
-        <v>60</v>
+        <v>110</v>
       </c>
       <c r="C38" t="s">
-        <v>42</v>
+        <v>117</v>
       </c>
       <c r="D38">
         <f>VLOOKUP(B38,Teams!A:B,2,FALSE)</f>
@@ -1754,18 +1760,18 @@
         <v>4</v>
       </c>
       <c r="F38" s="3" t="s">
-        <v>162</v>
+        <v>168</v>
       </c>
     </row>
     <row r="39" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A39" s="2">
-        <v>46284</v>
+        <v>46319</v>
       </c>
       <c r="B39" t="s">
-        <v>93</v>
+        <v>146</v>
       </c>
       <c r="C39" t="s">
-        <v>110</v>
+        <v>102</v>
       </c>
       <c r="D39">
         <f>VLOOKUP(B39,Teams!A:B,2,FALSE)</f>
@@ -1776,30 +1782,11 @@
         <v>4</v>
       </c>
       <c r="F39" s="3" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
     </row>
     <row r="40" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A40" s="2">
-        <v>46284</v>
-      </c>
-      <c r="B40" t="s">
-        <v>112</v>
-      </c>
-      <c r="C40" t="s">
-        <v>129</v>
-      </c>
-      <c r="D40">
-        <f>VLOOKUP(B40,Teams!A:B,2,FALSE)</f>
-        <v>4</v>
-      </c>
-      <c r="E40">
-        <f>VLOOKUP(C40,Teams!A:B,2,FALSE)</f>
-        <v>4</v>
-      </c>
-      <c r="F40" s="3" t="s">
-        <v>155</v>
-      </c>
+      <c r="A40" s="2"/>
     </row>
     <row r="41" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A41" s="2"/>

--- a/.github/tmp_results.xlsx
+++ b/.github/tmp_results.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Sean Elvidge\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6055D06B-3F36-4C70-B3D7-7A8027DCA24C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F29D43D0-0E46-417A-AFB9-F672820AC978}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="9510" yWindow="0" windowWidth="9780" windowHeight="11370" xr2:uid="{156B8CF3-2535-45A6-80D2-358CC30668D6}"/>
+    <workbookView xWindow="380" yWindow="380" windowWidth="11800" windowHeight="10070" xr2:uid="{156B8CF3-2535-45A6-80D2-358CC30668D6}"/>
   </bookViews>
   <sheets>
     <sheet name="Scores" sheetId="1" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="322" uniqueCount="169">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="214" uniqueCount="156">
   <si>
     <t>AFC Bournemouth</t>
   </si>
@@ -504,46 +504,7 @@
     <t>1-1</t>
   </si>
   <si>
-    <t>1-0</t>
-  </si>
-  <si>
-    <t>2-1</t>
-  </si>
-  <si>
-    <t>0-1</t>
-  </si>
-  <si>
-    <t>0-0</t>
-  </si>
-  <si>
-    <t>2-3</t>
-  </si>
-  <si>
-    <t>2-0</t>
-  </si>
-  <si>
-    <t>0-2</t>
-  </si>
-  <si>
-    <t>1-3</t>
-  </si>
-  <si>
-    <t>4-1</t>
-  </si>
-  <si>
-    <t>5-0</t>
-  </si>
-  <si>
-    <t>1-4</t>
-  </si>
-  <si>
-    <t>5-1</t>
-  </si>
-  <si>
-    <t>0-5</t>
-  </si>
-  <si>
-    <t>3-3</t>
+    <t>1-5</t>
   </si>
 </sst>
 </file>
@@ -951,13 +912,13 @@
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A2" s="2">
-        <v>46319</v>
+        <v>46318</v>
       </c>
       <c r="B2" t="s">
-        <v>9</v>
+        <v>67</v>
       </c>
       <c r="C2" t="s">
-        <v>79</v>
+        <v>96</v>
       </c>
       <c r="D2">
         <f>VLOOKUP(B2,Teams!A:B,2,FALSE)</f>
@@ -968,839 +929,155 @@
         <v>1</v>
       </c>
       <c r="F2" s="3" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A3" s="2">
-        <v>46319</v>
+        <v>46318</v>
       </c>
       <c r="B3" t="s">
-        <v>7</v>
+        <v>16</v>
       </c>
       <c r="C3" t="s">
-        <v>51</v>
+        <v>83</v>
       </c>
       <c r="D3">
         <f>VLOOKUP(B3,Teams!A:B,2,FALSE)</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E3">
         <f>VLOOKUP(C3,Teams!A:B,2,FALSE)</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>160</v>
+        <v>155</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A4" s="2">
-        <v>46319</v>
-      </c>
-      <c r="B4" t="s">
-        <v>41</v>
-      </c>
-      <c r="C4" t="s">
-        <v>55</v>
-      </c>
-      <c r="D4">
-        <f>VLOOKUP(B4,Teams!A:B,2,FALSE)</f>
-        <v>1</v>
-      </c>
-      <c r="E4">
-        <f>VLOOKUP(C4,Teams!A:B,2,FALSE)</f>
-        <v>1</v>
-      </c>
-      <c r="F4" s="3" t="s">
-        <v>157</v>
-      </c>
+      <c r="A4" s="2"/>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A5" s="2">
-        <v>46319</v>
-      </c>
-      <c r="B5" t="s">
-        <v>36</v>
-      </c>
-      <c r="C5" t="s">
-        <v>132</v>
-      </c>
-      <c r="D5">
-        <f>VLOOKUP(B5,Teams!A:B,2,FALSE)</f>
-        <v>1</v>
-      </c>
-      <c r="E5">
-        <f>VLOOKUP(C5,Teams!A:B,2,FALSE)</f>
-        <v>1</v>
-      </c>
-      <c r="F5" s="3" t="s">
-        <v>161</v>
-      </c>
+      <c r="A5" s="2"/>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A6" s="2">
-        <v>46319</v>
-      </c>
-      <c r="B6" t="s">
-        <v>35</v>
-      </c>
-      <c r="C6" t="s">
-        <v>95</v>
-      </c>
-      <c r="D6">
-        <f>VLOOKUP(B6,Teams!A:B,2,FALSE)</f>
-        <v>2</v>
-      </c>
-      <c r="E6">
-        <f>VLOOKUP(C6,Teams!A:B,2,FALSE)</f>
-        <v>2</v>
-      </c>
-      <c r="F6" s="3" t="s">
-        <v>162</v>
-      </c>
+      <c r="A6" s="2"/>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A7" s="2">
-        <v>46319</v>
-      </c>
-      <c r="B7" t="s">
-        <v>103</v>
-      </c>
-      <c r="C7" t="s">
-        <v>85</v>
-      </c>
-      <c r="D7">
-        <f>VLOOKUP(B7,Teams!A:B,2,FALSE)</f>
-        <v>2</v>
-      </c>
-      <c r="E7">
-        <f>VLOOKUP(C7,Teams!A:B,2,FALSE)</f>
-        <v>2</v>
-      </c>
-      <c r="F7" s="3" t="s">
-        <v>156</v>
-      </c>
+      <c r="A7" s="2"/>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A8" s="2">
-        <v>46319</v>
-      </c>
-      <c r="B8" t="s">
-        <v>115</v>
-      </c>
-      <c r="C8" t="s">
-        <v>48</v>
-      </c>
-      <c r="D8">
-        <f>VLOOKUP(B8,Teams!A:B,2,FALSE)</f>
-        <v>2</v>
-      </c>
-      <c r="E8">
-        <f>VLOOKUP(C8,Teams!A:B,2,FALSE)</f>
-        <v>2</v>
-      </c>
-      <c r="F8" s="3" t="s">
-        <v>154</v>
-      </c>
+      <c r="A8" s="2"/>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A9" s="2">
-        <v>46319</v>
-      </c>
-      <c r="B9" t="s">
-        <v>14</v>
-      </c>
-      <c r="C9" t="s">
-        <v>143</v>
-      </c>
-      <c r="D9">
-        <f>VLOOKUP(B9,Teams!A:B,2,FALSE)</f>
-        <v>2</v>
-      </c>
-      <c r="E9">
-        <f>VLOOKUP(C9,Teams!A:B,2,FALSE)</f>
-        <v>2</v>
-      </c>
-      <c r="F9" s="3" t="s">
-        <v>160</v>
-      </c>
+      <c r="A9" s="2"/>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A10" s="2">
-        <v>46319</v>
-      </c>
-      <c r="B10" t="s">
-        <v>33</v>
-      </c>
-      <c r="C10" t="s">
-        <v>13</v>
-      </c>
-      <c r="D10">
-        <f>VLOOKUP(B10,Teams!A:B,2,FALSE)</f>
-        <v>2</v>
-      </c>
-      <c r="E10">
-        <f>VLOOKUP(C10,Teams!A:B,2,FALSE)</f>
-        <v>2</v>
-      </c>
-      <c r="F10" s="3" t="s">
-        <v>155</v>
-      </c>
+      <c r="A10" s="2"/>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A11" s="2">
-        <v>46319</v>
-      </c>
-      <c r="B11" t="s">
-        <v>73</v>
-      </c>
-      <c r="C11" t="s">
-        <v>26</v>
-      </c>
-      <c r="D11">
-        <f>VLOOKUP(B11,Teams!A:B,2,FALSE)</f>
-        <v>2</v>
-      </c>
-      <c r="E11">
-        <f>VLOOKUP(C11,Teams!A:B,2,FALSE)</f>
-        <v>2</v>
-      </c>
-      <c r="F11" s="3" t="s">
-        <v>163</v>
-      </c>
+      <c r="A11" s="2"/>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A12" s="2">
-        <v>46319</v>
-      </c>
-      <c r="B12" t="s">
-        <v>104</v>
-      </c>
-      <c r="C12" t="s">
-        <v>136</v>
-      </c>
-      <c r="D12">
-        <f>VLOOKUP(B12,Teams!A:B,2,FALSE)</f>
-        <v>2</v>
-      </c>
-      <c r="E12">
-        <f>VLOOKUP(C12,Teams!A:B,2,FALSE)</f>
-        <v>2</v>
-      </c>
-      <c r="F12" s="3" t="s">
-        <v>154</v>
-      </c>
+      <c r="A12" s="2"/>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A13" s="2">
-        <v>46319</v>
-      </c>
-      <c r="B13" t="s">
-        <v>105</v>
-      </c>
-      <c r="C13" t="s">
-        <v>128</v>
-      </c>
-      <c r="D13">
-        <f>VLOOKUP(B13,Teams!A:B,2,FALSE)</f>
-        <v>2</v>
-      </c>
-      <c r="E13">
-        <f>VLOOKUP(C13,Teams!A:B,2,FALSE)</f>
-        <v>2</v>
-      </c>
-      <c r="F13" s="3" t="s">
-        <v>164</v>
-      </c>
+      <c r="A13" s="2"/>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A14" s="2">
-        <v>46319</v>
-      </c>
-      <c r="B14" t="s">
-        <v>125</v>
-      </c>
-      <c r="C14" t="s">
-        <v>23</v>
-      </c>
-      <c r="D14">
-        <f>VLOOKUP(B14,Teams!A:B,2,FALSE)</f>
-        <v>2</v>
-      </c>
-      <c r="E14">
-        <f>VLOOKUP(C14,Teams!A:B,2,FALSE)</f>
-        <v>2</v>
-      </c>
-      <c r="F14" s="3" t="s">
-        <v>158</v>
-      </c>
+      <c r="A14" s="2"/>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A15" s="2">
-        <v>46319</v>
-      </c>
-      <c r="B15" t="s">
-        <v>137</v>
-      </c>
-      <c r="C15" t="s">
-        <v>119</v>
-      </c>
-      <c r="D15">
-        <f>VLOOKUP(B15,Teams!A:B,2,FALSE)</f>
-        <v>2</v>
-      </c>
-      <c r="E15">
-        <f>VLOOKUP(C15,Teams!A:B,2,FALSE)</f>
-        <v>2</v>
-      </c>
-      <c r="F15" s="3" t="s">
-        <v>159</v>
-      </c>
+      <c r="A15" s="2"/>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A16" s="2">
-        <v>46319</v>
-      </c>
-      <c r="B16" t="s">
-        <v>141</v>
-      </c>
-      <c r="C16" t="s">
-        <v>135</v>
-      </c>
-      <c r="D16">
-        <f>VLOOKUP(B16,Teams!A:B,2,FALSE)</f>
-        <v>2</v>
-      </c>
-      <c r="E16">
-        <f>VLOOKUP(C16,Teams!A:B,2,FALSE)</f>
-        <v>2</v>
-      </c>
-      <c r="F16" s="3" t="s">
-        <v>155</v>
-      </c>
-    </row>
-    <row r="17" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A17" s="2">
-        <v>46319</v>
-      </c>
-      <c r="B17" t="s">
-        <v>65</v>
-      </c>
-      <c r="C17" t="s">
-        <v>138</v>
-      </c>
-      <c r="D17">
-        <f>VLOOKUP(B17,Teams!A:B,2,FALSE)</f>
-        <v>3</v>
-      </c>
-      <c r="E17">
-        <f>VLOOKUP(C17,Teams!A:B,2,FALSE)</f>
-        <v>3</v>
-      </c>
-      <c r="F17" s="3" t="s">
-        <v>156</v>
-      </c>
-    </row>
-    <row r="18" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A18" s="2">
-        <v>46319</v>
-      </c>
-      <c r="B18" t="s">
-        <v>76</v>
-      </c>
-      <c r="C18" t="s">
-        <v>71</v>
-      </c>
-      <c r="D18">
-        <f>VLOOKUP(B18,Teams!A:B,2,FALSE)</f>
-        <v>3</v>
-      </c>
-      <c r="E18">
-        <f>VLOOKUP(C18,Teams!A:B,2,FALSE)</f>
-        <v>3</v>
-      </c>
-      <c r="F18" s="3" t="s">
-        <v>156</v>
-      </c>
-    </row>
-    <row r="19" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A19" s="2">
-        <v>46319</v>
-      </c>
-      <c r="B19" t="s">
-        <v>1</v>
-      </c>
-      <c r="C19" t="s">
-        <v>144</v>
-      </c>
-      <c r="D19">
-        <f>VLOOKUP(B19,Teams!A:B,2,FALSE)</f>
-        <v>3</v>
-      </c>
-      <c r="E19">
-        <f>VLOOKUP(C19,Teams!A:B,2,FALSE)</f>
-        <v>3</v>
-      </c>
-      <c r="F19" s="3" t="s">
-        <v>154</v>
-      </c>
-    </row>
-    <row r="20" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A20" s="2">
-        <v>46319</v>
-      </c>
-      <c r="B20" t="s">
-        <v>15</v>
-      </c>
-      <c r="C20" t="s">
-        <v>81</v>
-      </c>
-      <c r="D20">
-        <f>VLOOKUP(B20,Teams!A:B,2,FALSE)</f>
-        <v>3</v>
-      </c>
-      <c r="E20">
-        <f>VLOOKUP(C20,Teams!A:B,2,FALSE)</f>
-        <v>3</v>
-      </c>
-      <c r="F20" s="3" t="s">
-        <v>165</v>
-      </c>
-    </row>
-    <row r="21" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A21" s="2">
-        <v>46319</v>
-      </c>
-      <c r="B21" t="s">
-        <v>25</v>
-      </c>
-      <c r="C21" t="s">
-        <v>100</v>
-      </c>
-      <c r="D21">
-        <f>VLOOKUP(B21,Teams!A:B,2,FALSE)</f>
-        <v>3</v>
-      </c>
-      <c r="E21">
-        <f>VLOOKUP(C21,Teams!A:B,2,FALSE)</f>
-        <v>3</v>
-      </c>
-      <c r="F21" s="3" t="s">
-        <v>154</v>
-      </c>
-    </row>
-    <row r="22" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A22" s="2">
-        <v>46319</v>
-      </c>
-      <c r="B22" t="s">
-        <v>27</v>
-      </c>
-      <c r="C22" t="s">
-        <v>72</v>
-      </c>
-      <c r="D22">
-        <f>VLOOKUP(B22,Teams!A:B,2,FALSE)</f>
-        <v>3</v>
-      </c>
-      <c r="E22">
-        <f>VLOOKUP(C22,Teams!A:B,2,FALSE)</f>
-        <v>3</v>
-      </c>
-      <c r="F22" s="3" t="s">
-        <v>156</v>
-      </c>
-    </row>
-    <row r="23" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A23" s="2">
-        <v>46319</v>
-      </c>
-      <c r="B23" t="s">
-        <v>32</v>
-      </c>
-      <c r="C23" t="s">
-        <v>101</v>
-      </c>
-      <c r="D23">
-        <f>VLOOKUP(B23,Teams!A:B,2,FALSE)</f>
-        <v>3</v>
-      </c>
-      <c r="E23">
-        <f>VLOOKUP(C23,Teams!A:B,2,FALSE)</f>
-        <v>3</v>
-      </c>
-      <c r="F23" s="3" t="s">
-        <v>159</v>
-      </c>
-    </row>
-    <row r="24" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A24" s="2">
-        <v>46319</v>
-      </c>
-      <c r="B24" t="s">
-        <v>49</v>
-      </c>
-      <c r="C24" t="s">
-        <v>116</v>
-      </c>
-      <c r="D24">
-        <f>VLOOKUP(B24,Teams!A:B,2,FALSE)</f>
-        <v>3</v>
-      </c>
-      <c r="E24">
-        <f>VLOOKUP(C24,Teams!A:B,2,FALSE)</f>
-        <v>3</v>
-      </c>
-      <c r="F24" s="3" t="s">
-        <v>160</v>
-      </c>
-    </row>
-    <row r="25" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A25" s="2">
-        <v>46319</v>
-      </c>
-      <c r="B25" t="s">
-        <v>97</v>
-      </c>
-      <c r="C25" t="s">
-        <v>124</v>
-      </c>
-      <c r="D25">
-        <f>VLOOKUP(B25,Teams!A:B,2,FALSE)</f>
-        <v>3</v>
-      </c>
-      <c r="E25">
-        <f>VLOOKUP(C25,Teams!A:B,2,FALSE)</f>
-        <v>3</v>
-      </c>
-      <c r="F25" s="3" t="s">
-        <v>154</v>
-      </c>
-    </row>
-    <row r="26" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A26" s="2">
-        <v>46319</v>
-      </c>
-      <c r="B26" t="s">
-        <v>99</v>
-      </c>
-      <c r="C26" t="s">
-        <v>19</v>
-      </c>
-      <c r="D26">
-        <f>VLOOKUP(B26,Teams!A:B,2,FALSE)</f>
-        <v>3</v>
-      </c>
-      <c r="E26">
-        <f>VLOOKUP(C26,Teams!A:B,2,FALSE)</f>
-        <v>3</v>
-      </c>
-      <c r="F26" s="3" t="s">
-        <v>158</v>
-      </c>
-    </row>
-    <row r="27" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A27" s="2">
-        <v>46319</v>
-      </c>
-      <c r="B27" t="s">
-        <v>106</v>
-      </c>
-      <c r="C27" t="s">
-        <v>11</v>
-      </c>
-      <c r="D27">
-        <f>VLOOKUP(B27,Teams!A:B,2,FALSE)</f>
-        <v>3</v>
-      </c>
-      <c r="E27">
-        <f>VLOOKUP(C27,Teams!A:B,2,FALSE)</f>
-        <v>3</v>
-      </c>
-      <c r="F27" s="3" t="s">
-        <v>156</v>
-      </c>
-    </row>
-    <row r="28" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A28" s="2">
-        <v>46319</v>
-      </c>
-      <c r="B28" t="s">
-        <v>123</v>
-      </c>
-      <c r="C28" t="s">
-        <v>86</v>
-      </c>
-      <c r="D28">
-        <f>VLOOKUP(B28,Teams!A:B,2,FALSE)</f>
-        <v>3</v>
-      </c>
-      <c r="E28">
-        <f>VLOOKUP(C28,Teams!A:B,2,FALSE)</f>
-        <v>3</v>
-      </c>
-      <c r="F28" s="3" t="s">
-        <v>157</v>
-      </c>
-    </row>
-    <row r="29" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A29" s="2">
-        <v>46319</v>
-      </c>
-      <c r="B29" t="s">
-        <v>24</v>
-      </c>
-      <c r="C29" t="s">
-        <v>129</v>
-      </c>
-      <c r="D29">
-        <f>VLOOKUP(B29,Teams!A:B,2,FALSE)</f>
-        <v>4</v>
-      </c>
-      <c r="E29">
-        <f>VLOOKUP(C29,Teams!A:B,2,FALSE)</f>
-        <v>4</v>
-      </c>
-      <c r="F29" s="3" t="s">
-        <v>158</v>
-      </c>
-    </row>
-    <row r="30" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A30" s="2">
-        <v>46319</v>
-      </c>
-      <c r="B30" t="s">
-        <v>37</v>
-      </c>
-      <c r="C30" t="s">
-        <v>92</v>
-      </c>
-      <c r="D30">
-        <f>VLOOKUP(B30,Teams!A:B,2,FALSE)</f>
-        <v>4</v>
-      </c>
-      <c r="E30">
-        <f>VLOOKUP(C30,Teams!A:B,2,FALSE)</f>
-        <v>4</v>
-      </c>
-      <c r="F30" s="3" t="s">
-        <v>155</v>
-      </c>
-    </row>
-    <row r="31" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A31" s="2">
-        <v>46319</v>
-      </c>
-      <c r="B31" t="s">
-        <v>93</v>
-      </c>
-      <c r="C31" t="s">
-        <v>40</v>
-      </c>
-      <c r="D31">
-        <f>VLOOKUP(B31,Teams!A:B,2,FALSE)</f>
-        <v>4</v>
-      </c>
-      <c r="E31">
-        <f>VLOOKUP(C31,Teams!A:B,2,FALSE)</f>
-        <v>4</v>
-      </c>
-      <c r="F31" s="3" t="s">
-        <v>160</v>
-      </c>
-    </row>
-    <row r="32" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A32" s="2">
-        <v>46319</v>
-      </c>
-      <c r="B32" t="s">
-        <v>10</v>
-      </c>
-      <c r="C32" t="s">
-        <v>98</v>
-      </c>
-      <c r="D32">
-        <f>VLOOKUP(B32,Teams!A:B,2,FALSE)</f>
-        <v>4</v>
-      </c>
-      <c r="E32">
-        <f>VLOOKUP(C32,Teams!A:B,2,FALSE)</f>
-        <v>4</v>
-      </c>
-      <c r="F32" s="3" t="s">
-        <v>154</v>
-      </c>
-    </row>
-    <row r="33" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A33" s="2">
-        <v>46319</v>
-      </c>
-      <c r="B33" t="s">
-        <v>39</v>
-      </c>
-      <c r="C33" t="s">
-        <v>43</v>
-      </c>
-      <c r="D33">
-        <f>VLOOKUP(B33,Teams!A:B,2,FALSE)</f>
-        <v>4</v>
-      </c>
-      <c r="E33">
-        <f>VLOOKUP(C33,Teams!A:B,2,FALSE)</f>
-        <v>4</v>
-      </c>
-      <c r="F33" s="3" t="s">
-        <v>166</v>
-      </c>
-    </row>
-    <row r="34" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A34" s="2">
-        <v>46319</v>
-      </c>
-      <c r="B34" t="s">
-        <v>42</v>
-      </c>
-      <c r="C34" t="s">
-        <v>133</v>
-      </c>
-      <c r="D34">
-        <f>VLOOKUP(B34,Teams!A:B,2,FALSE)</f>
-        <v>4</v>
-      </c>
-      <c r="E34">
-        <f>VLOOKUP(C34,Teams!A:B,2,FALSE)</f>
-        <v>4</v>
-      </c>
-      <c r="F34" s="3" t="s">
-        <v>154</v>
-      </c>
-    </row>
-    <row r="35" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A35" s="2">
-        <v>46319</v>
-      </c>
-      <c r="B35" t="s">
-        <v>52</v>
-      </c>
-      <c r="C35" t="s">
-        <v>53</v>
-      </c>
-      <c r="D35">
-        <f>VLOOKUP(B35,Teams!A:B,2,FALSE)</f>
-        <v>4</v>
-      </c>
-      <c r="E35">
-        <f>VLOOKUP(C35,Teams!A:B,2,FALSE)</f>
-        <v>4</v>
-      </c>
-      <c r="F35" s="3" t="s">
-        <v>156</v>
-      </c>
-    </row>
-    <row r="36" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A36" s="2">
-        <v>46319</v>
-      </c>
-      <c r="B36" t="s">
-        <v>58</v>
-      </c>
-      <c r="C36" t="s">
-        <v>60</v>
-      </c>
-      <c r="D36">
-        <f>VLOOKUP(B36,Teams!A:B,2,FALSE)</f>
-        <v>4</v>
-      </c>
-      <c r="E36">
-        <f>VLOOKUP(C36,Teams!A:B,2,FALSE)</f>
-        <v>4</v>
-      </c>
-      <c r="F36" s="3" t="s">
-        <v>165</v>
-      </c>
-    </row>
-    <row r="37" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A37" s="2">
-        <v>46319</v>
-      </c>
-      <c r="B37" t="s">
-        <v>107</v>
-      </c>
-      <c r="C37" t="s">
-        <v>4</v>
-      </c>
-      <c r="D37">
-        <f>VLOOKUP(B37,Teams!A:B,2,FALSE)</f>
-        <v>4</v>
-      </c>
-      <c r="E37">
-        <f>VLOOKUP(C37,Teams!A:B,2,FALSE)</f>
-        <v>4</v>
-      </c>
-      <c r="F37" s="3" t="s">
-        <v>167</v>
-      </c>
-    </row>
-    <row r="38" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A38" s="2">
-        <v>46319</v>
-      </c>
-      <c r="B38" t="s">
-        <v>110</v>
-      </c>
-      <c r="C38" t="s">
-        <v>117</v>
-      </c>
-      <c r="D38">
-        <f>VLOOKUP(B38,Teams!A:B,2,FALSE)</f>
-        <v>4</v>
-      </c>
-      <c r="E38">
-        <f>VLOOKUP(C38,Teams!A:B,2,FALSE)</f>
-        <v>4</v>
-      </c>
-      <c r="F38" s="3" t="s">
-        <v>168</v>
-      </c>
-    </row>
-    <row r="39" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A39" s="2">
-        <v>46319</v>
-      </c>
-      <c r="B39" t="s">
-        <v>146</v>
-      </c>
-      <c r="C39" t="s">
-        <v>102</v>
-      </c>
-      <c r="D39">
-        <f>VLOOKUP(B39,Teams!A:B,2,FALSE)</f>
-        <v>4</v>
-      </c>
-      <c r="E39">
-        <f>VLOOKUP(C39,Teams!A:B,2,FALSE)</f>
-        <v>4</v>
-      </c>
-      <c r="F39" s="3" t="s">
-        <v>160</v>
-      </c>
-    </row>
-    <row r="40" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A16" s="2"/>
+    </row>
+    <row r="17" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A17" s="2"/>
+    </row>
+    <row r="18" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A18" s="2"/>
+    </row>
+    <row r="19" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A19" s="2"/>
+    </row>
+    <row r="20" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A20" s="2"/>
+    </row>
+    <row r="21" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A21" s="2"/>
+    </row>
+    <row r="22" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A22" s="2"/>
+    </row>
+    <row r="23" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A23" s="2"/>
+    </row>
+    <row r="24" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A24" s="2"/>
+    </row>
+    <row r="25" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A25" s="2"/>
+    </row>
+    <row r="26" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A26" s="2"/>
+    </row>
+    <row r="27" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A27" s="2"/>
+    </row>
+    <row r="28" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A28" s="2"/>
+    </row>
+    <row r="29" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A29" s="2"/>
+    </row>
+    <row r="30" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A30" s="2"/>
+    </row>
+    <row r="31" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A31" s="2"/>
+    </row>
+    <row r="32" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A32" s="2"/>
+    </row>
+    <row r="33" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A33" s="2"/>
+    </row>
+    <row r="34" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A34" s="2"/>
+    </row>
+    <row r="35" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A35" s="2"/>
+    </row>
+    <row r="36" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A36" s="2"/>
+    </row>
+    <row r="37" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A37" s="2"/>
+    </row>
+    <row r="38" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A38" s="2"/>
+    </row>
+    <row r="39" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A39" s="2"/>
+    </row>
+    <row r="40" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A40" s="2"/>
     </row>
-    <row r="41" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="41" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A41" s="2"/>
     </row>
-    <row r="42" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="42" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A42" s="2"/>
     </row>
-    <row r="43" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="43" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A43" s="2"/>
     </row>
-    <row r="44" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="44" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A44" s="2"/>
     </row>
-    <row r="45" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="45" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A45" s="2"/>
     </row>
   </sheetData>

--- a/.github/tmp_results.xlsx
+++ b/.github/tmp_results.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Sean Elvidge\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F29D43D0-0E46-417A-AFB9-F672820AC978}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DB7B6ABE-32E6-4EBE-9976-597C86A14702}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="380" yWindow="380" windowWidth="11800" windowHeight="10070" xr2:uid="{156B8CF3-2535-45A6-80D2-358CC30668D6}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="214" uniqueCount="156">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="223" uniqueCount="159">
   <si>
     <t>AFC Bournemouth</t>
   </si>
@@ -504,7 +504,16 @@
     <t>1-1</t>
   </si>
   <si>
-    <t>1-5</t>
+    <t>0-2</t>
+  </si>
+  <si>
+    <t>2-0</t>
+  </si>
+  <si>
+    <t>0-3</t>
+  </si>
+  <si>
+    <t>0-0</t>
   </si>
 </sst>
 </file>
@@ -912,13 +921,13 @@
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A2" s="2">
-        <v>46318</v>
+        <v>46320</v>
       </c>
       <c r="B2" t="s">
-        <v>67</v>
+        <v>44</v>
       </c>
       <c r="C2" t="s">
-        <v>96</v>
+        <v>91</v>
       </c>
       <c r="D2">
         <f>VLOOKUP(B2,Teams!A:B,2,FALSE)</f>
@@ -929,39 +938,96 @@
         <v>1</v>
       </c>
       <c r="F2" s="3" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A3" s="2">
-        <v>46318</v>
+        <v>46320</v>
       </c>
       <c r="B3" t="s">
-        <v>16</v>
+        <v>66</v>
       </c>
       <c r="C3" t="s">
-        <v>83</v>
+        <v>21</v>
       </c>
       <c r="D3">
         <f>VLOOKUP(B3,Teams!A:B,2,FALSE)</f>
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E3">
         <f>VLOOKUP(C3,Teams!A:B,2,FALSE)</f>
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A4" s="2"/>
+      <c r="A4" s="2">
+        <v>46320</v>
+      </c>
+      <c r="B4" t="s">
+        <v>74</v>
+      </c>
+      <c r="C4" t="s">
+        <v>22</v>
+      </c>
+      <c r="D4">
+        <f>VLOOKUP(B4,Teams!A:B,2,FALSE)</f>
+        <v>1</v>
+      </c>
+      <c r="E4">
+        <f>VLOOKUP(C4,Teams!A:B,2,FALSE)</f>
+        <v>1</v>
+      </c>
+      <c r="F4" s="3" t="s">
+        <v>156</v>
+      </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A5" s="2"/>
+      <c r="A5" s="2">
+        <v>46320</v>
+      </c>
+      <c r="B5" t="s">
+        <v>80</v>
+      </c>
+      <c r="C5" t="s">
+        <v>0</v>
+      </c>
+      <c r="D5">
+        <f>VLOOKUP(B5,Teams!A:B,2,FALSE)</f>
+        <v>1</v>
+      </c>
+      <c r="E5">
+        <f>VLOOKUP(C5,Teams!A:B,2,FALSE)</f>
+        <v>1</v>
+      </c>
+      <c r="F5" s="3" t="s">
+        <v>157</v>
+      </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A6" s="2"/>
+      <c r="A6" s="2">
+        <v>46320</v>
+      </c>
+      <c r="B6" t="s">
+        <v>126</v>
+      </c>
+      <c r="C6" t="s">
+        <v>70</v>
+      </c>
+      <c r="D6">
+        <f>VLOOKUP(B6,Teams!A:B,2,FALSE)</f>
+        <v>1</v>
+      </c>
+      <c r="E6">
+        <f>VLOOKUP(C6,Teams!A:B,2,FALSE)</f>
+        <v>1</v>
+      </c>
+      <c r="F6" s="3" t="s">
+        <v>158</v>
+      </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A7" s="2"/>

--- a/.github/tmp_results.xlsx
+++ b/.github/tmp_results.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30430"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30527"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Sean Elvidge\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DB7B6ABE-32E6-4EBE-9976-597C86A14702}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B7A37A63-1A12-4767-873E-AF57537725B6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="380" yWindow="380" windowWidth="11800" windowHeight="10070" xr2:uid="{156B8CF3-2535-45A6-80D2-358CC30668D6}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="223" uniqueCount="159">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="211" uniqueCount="155">
   <si>
     <t>AFC Bournemouth</t>
   </si>
@@ -501,19 +501,7 @@
     <t>Tier Ch</t>
   </si>
   <si>
-    <t>1-1</t>
-  </si>
-  <si>
-    <t>0-2</t>
-  </si>
-  <si>
-    <t>2-0</t>
-  </si>
-  <si>
-    <t>0-3</t>
-  </si>
-  <si>
-    <t>0-0</t>
+    <t>2-4</t>
   </si>
 </sst>
 </file>
@@ -921,113 +909,37 @@
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A2" s="2">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="B2" t="s">
-        <v>44</v>
+        <v>134</v>
       </c>
       <c r="C2" t="s">
-        <v>91</v>
+        <v>112</v>
       </c>
       <c r="D2">
         <f>VLOOKUP(B2,Teams!A:B,2,FALSE)</f>
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E2">
         <f>VLOOKUP(C2,Teams!A:B,2,FALSE)</f>
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F2" s="3" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A3" s="2">
-        <v>46320</v>
-      </c>
-      <c r="B3" t="s">
-        <v>66</v>
-      </c>
-      <c r="C3" t="s">
-        <v>21</v>
-      </c>
-      <c r="D3">
-        <f>VLOOKUP(B3,Teams!A:B,2,FALSE)</f>
-        <v>1</v>
-      </c>
-      <c r="E3">
-        <f>VLOOKUP(C3,Teams!A:B,2,FALSE)</f>
-        <v>1</v>
-      </c>
-      <c r="F3" s="3" t="s">
-        <v>154</v>
-      </c>
+      <c r="A3" s="2"/>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A4" s="2">
-        <v>46320</v>
-      </c>
-      <c r="B4" t="s">
-        <v>74</v>
-      </c>
-      <c r="C4" t="s">
-        <v>22</v>
-      </c>
-      <c r="D4">
-        <f>VLOOKUP(B4,Teams!A:B,2,FALSE)</f>
-        <v>1</v>
-      </c>
-      <c r="E4">
-        <f>VLOOKUP(C4,Teams!A:B,2,FALSE)</f>
-        <v>1</v>
-      </c>
-      <c r="F4" s="3" t="s">
-        <v>156</v>
-      </c>
+      <c r="A4" s="2"/>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A5" s="2">
-        <v>46320</v>
-      </c>
-      <c r="B5" t="s">
-        <v>80</v>
-      </c>
-      <c r="C5" t="s">
-        <v>0</v>
-      </c>
-      <c r="D5">
-        <f>VLOOKUP(B5,Teams!A:B,2,FALSE)</f>
-        <v>1</v>
-      </c>
-      <c r="E5">
-        <f>VLOOKUP(C5,Teams!A:B,2,FALSE)</f>
-        <v>1</v>
-      </c>
-      <c r="F5" s="3" t="s">
-        <v>157</v>
-      </c>
+      <c r="A5" s="2"/>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A6" s="2">
-        <v>46320</v>
-      </c>
-      <c r="B6" t="s">
-        <v>126</v>
-      </c>
-      <c r="C6" t="s">
-        <v>70</v>
-      </c>
-      <c r="D6">
-        <f>VLOOKUP(B6,Teams!A:B,2,FALSE)</f>
-        <v>1</v>
-      </c>
-      <c r="E6">
-        <f>VLOOKUP(C6,Teams!A:B,2,FALSE)</f>
-        <v>1</v>
-      </c>
-      <c r="F6" s="3" t="s">
-        <v>158</v>
-      </c>
+      <c r="A6" s="2"/>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A7" s="2"/>

--- a/.github/tmp_results.xlsx
+++ b/.github/tmp_results.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Sean Elvidge\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\elvidgsm\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B7A37A63-1A12-4767-873E-AF57537725B6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4885E51A-851C-4377-BA46-B18BAD862E50}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="380" yWindow="380" windowWidth="11800" windowHeight="10070" xr2:uid="{156B8CF3-2535-45A6-80D2-358CC30668D6}"/>
+    <workbookView xWindow="30315" yWindow="3480" windowWidth="15660" windowHeight="11820" xr2:uid="{156B8CF3-2535-45A6-80D2-358CC30668D6}"/>
   </bookViews>
   <sheets>
     <sheet name="Scores" sheetId="1" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="211" uniqueCount="155">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="226" uniqueCount="159">
   <si>
     <t>AFC Bournemouth</t>
   </si>
@@ -501,7 +501,19 @@
     <t>Tier Ch</t>
   </si>
   <si>
-    <t>2-4</t>
+    <t>3-0</t>
+  </si>
+  <si>
+    <t>4-1</t>
+  </si>
+  <si>
+    <t>3-1</t>
+  </si>
+  <si>
+    <t>1-0</t>
+  </si>
+  <si>
+    <t>1-1</t>
   </si>
 </sst>
 </file>
@@ -879,15 +891,15 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{944D37C4-CAD2-4526-8947-361FF9BC37B9}">
   <dimension ref="A1:F45"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="10.54296875" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="18.81640625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="10.5703125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="18.85546875" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="23" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="8.7265625" style="3"/>
+    <col min="6" max="6" width="8.7109375" style="3"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>149</v>
       </c>
@@ -907,155 +919,250 @@
         <v>152</v>
       </c>
     </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2" s="2">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="B2" t="s">
-        <v>134</v>
+        <v>71</v>
       </c>
       <c r="C2" t="s">
-        <v>112</v>
+        <v>138</v>
       </c>
       <c r="D2">
         <f>VLOOKUP(B2,Teams!A:B,2,FALSE)</f>
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E2">
         <f>VLOOKUP(C2,Teams!A:B,2,FALSE)</f>
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F2" s="3" t="s">
         <v>154</v>
       </c>
     </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A3" s="2"/>
-    </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A4" s="2"/>
-    </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A5" s="2"/>
-    </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A6" s="2"/>
-    </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A7" s="2"/>
-    </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A3" s="2">
+        <v>46322</v>
+      </c>
+      <c r="B3" t="s">
+        <v>86</v>
+      </c>
+      <c r="C3" t="s">
+        <v>25</v>
+      </c>
+      <c r="D3">
+        <f>VLOOKUP(B3,Teams!A:B,2,FALSE)</f>
+        <v>3</v>
+      </c>
+      <c r="E3">
+        <f>VLOOKUP(C3,Teams!A:B,2,FALSE)</f>
+        <v>3</v>
+      </c>
+      <c r="F3" s="3" t="s">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A4" s="2">
+        <v>46322</v>
+      </c>
+      <c r="B4" t="s">
+        <v>76</v>
+      </c>
+      <c r="C4" t="s">
+        <v>49</v>
+      </c>
+      <c r="D4">
+        <f>VLOOKUP(B4,Teams!A:B,2,FALSE)</f>
+        <v>3</v>
+      </c>
+      <c r="E4">
+        <f>VLOOKUP(C4,Teams!A:B,2,FALSE)</f>
+        <v>3</v>
+      </c>
+      <c r="F4" s="3" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A5" s="2">
+        <v>46322</v>
+      </c>
+      <c r="B5" t="s">
+        <v>99</v>
+      </c>
+      <c r="C5" t="s">
+        <v>124</v>
+      </c>
+      <c r="D5">
+        <f>VLOOKUP(B5,Teams!A:B,2,FALSE)</f>
+        <v>3</v>
+      </c>
+      <c r="E5">
+        <f>VLOOKUP(C5,Teams!A:B,2,FALSE)</f>
+        <v>3</v>
+      </c>
+      <c r="F5" s="3" t="s">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A6" s="2">
+        <v>46322</v>
+      </c>
+      <c r="B6" t="s">
+        <v>116</v>
+      </c>
+      <c r="C6" t="s">
+        <v>32</v>
+      </c>
+      <c r="D6">
+        <f>VLOOKUP(B6,Teams!A:B,2,FALSE)</f>
+        <v>3</v>
+      </c>
+      <c r="E6">
+        <f>VLOOKUP(C6,Teams!A:B,2,FALSE)</f>
+        <v>3</v>
+      </c>
+      <c r="F6" s="3" t="s">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A7" s="2">
+        <v>46322</v>
+      </c>
+      <c r="B7" t="s">
+        <v>10</v>
+      </c>
+      <c r="C7" t="s">
+        <v>146</v>
+      </c>
+      <c r="D7">
+        <f>VLOOKUP(B7,Teams!A:B,2,FALSE)</f>
+        <v>4</v>
+      </c>
+      <c r="E7">
+        <f>VLOOKUP(C7,Teams!A:B,2,FALSE)</f>
+        <v>4</v>
+      </c>
+      <c r="F7" s="3" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" s="2"/>
     </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" s="2"/>
     </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" s="2"/>
     </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" s="2"/>
     </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A12" s="2"/>
     </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A13" s="2"/>
     </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A14" s="2"/>
     </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A15" s="2"/>
     </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A16" s="2"/>
     </row>
-    <row r="17" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A17" s="2"/>
     </row>
-    <row r="18" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A18" s="2"/>
     </row>
-    <row r="19" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A19" s="2"/>
     </row>
-    <row r="20" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A20" s="2"/>
     </row>
-    <row r="21" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A21" s="2"/>
     </row>
-    <row r="22" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A22" s="2"/>
     </row>
-    <row r="23" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A23" s="2"/>
     </row>
-    <row r="24" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A24" s="2"/>
     </row>
-    <row r="25" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A25" s="2"/>
     </row>
-    <row r="26" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A26" s="2"/>
     </row>
-    <row r="27" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A27" s="2"/>
     </row>
-    <row r="28" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="28" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A28" s="2"/>
     </row>
-    <row r="29" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="29" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A29" s="2"/>
     </row>
-    <row r="30" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="30" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A30" s="2"/>
     </row>
-    <row r="31" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="31" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A31" s="2"/>
     </row>
-    <row r="32" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="32" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A32" s="2"/>
     </row>
-    <row r="33" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="33" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A33" s="2"/>
     </row>
-    <row r="34" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="34" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A34" s="2"/>
     </row>
-    <row r="35" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="35" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A35" s="2"/>
     </row>
-    <row r="36" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="36" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A36" s="2"/>
     </row>
-    <row r="37" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="37" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A37" s="2"/>
     </row>
-    <row r="38" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="38" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A38" s="2"/>
     </row>
-    <row r="39" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="39" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A39" s="2"/>
     </row>
-    <row r="40" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="40" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A40" s="2"/>
     </row>
-    <row r="41" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="41" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A41" s="2"/>
     </row>
-    <row r="42" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="42" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A42" s="2"/>
     </row>
-    <row r="43" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="43" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A43" s="2"/>
     </row>
-    <row r="44" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="44" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A44" s="2"/>
     </row>
-    <row r="45" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="45" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A45" s="2"/>
     </row>
   </sheetData>
@@ -1078,13 +1185,13 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{660D5CBD-EF61-4F28-8F5F-C3B953B1D14A}">
   <dimension ref="A1:B147"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="23" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="8.7265625" style="1"/>
+    <col min="2" max="2" width="8.7109375" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1092,7 +1199,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>1</v>
       </c>
@@ -1100,7 +1207,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>2</v>
       </c>
@@ -1108,7 +1215,7 @@
         <v>148</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>3</v>
       </c>
@@ -1116,7 +1223,7 @@
         <v>148</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>4</v>
       </c>
@@ -1124,7 +1231,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>5</v>
       </c>
@@ -1132,7 +1239,7 @@
         <v>148</v>
       </c>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>6</v>
       </c>
@@ -1140,7 +1247,7 @@
         <v>148</v>
       </c>
     </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>7</v>
       </c>
@@ -1148,7 +1255,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>8</v>
       </c>
@@ -1156,7 +1263,7 @@
         <v>148</v>
       </c>
     </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>9</v>
       </c>
@@ -1164,7 +1271,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>10</v>
       </c>
@@ -1172,7 +1279,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>11</v>
       </c>
@@ -1180,7 +1287,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>12</v>
       </c>
@@ -1188,7 +1295,7 @@
         <v>148</v>
       </c>
     </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>13</v>
       </c>
@@ -1196,7 +1303,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>14</v>
       </c>
@@ -1204,7 +1311,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="16" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>15</v>
       </c>
@@ -1212,7 +1319,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>16</v>
       </c>
@@ -1220,7 +1327,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>17</v>
       </c>
@@ -1228,7 +1335,7 @@
         <v>148</v>
       </c>
     </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>18</v>
       </c>
@@ -1236,7 +1343,7 @@
         <v>148</v>
       </c>
     </row>
-    <row r="20" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>19</v>
       </c>
@@ -1244,7 +1351,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="21" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>20</v>
       </c>
@@ -1252,7 +1359,7 @@
         <v>148</v>
       </c>
     </row>
-    <row r="22" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
         <v>21</v>
       </c>
@@ -1260,7 +1367,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="23" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
         <v>22</v>
       </c>
@@ -1268,7 +1375,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="24" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
         <v>23</v>
       </c>
@@ -1276,7 +1383,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="25" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
         <v>24</v>
       </c>
@@ -1284,7 +1391,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="26" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
         <v>25</v>
       </c>
@@ -1292,7 +1399,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="27" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
         <v>26</v>
       </c>
@@ -1300,7 +1407,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="28" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="28" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
         <v>27</v>
       </c>
@@ -1308,7 +1415,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="29" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="29" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
         <v>28</v>
       </c>
@@ -1316,7 +1423,7 @@
         <v>148</v>
       </c>
     </row>
-    <row r="30" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="30" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
         <v>29</v>
       </c>
@@ -1324,7 +1431,7 @@
         <v>148</v>
       </c>
     </row>
-    <row r="31" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="31" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
         <v>30</v>
       </c>
@@ -1332,7 +1439,7 @@
         <v>148</v>
       </c>
     </row>
-    <row r="32" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="32" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
         <v>31</v>
       </c>
@@ -1340,7 +1447,7 @@
         <v>148</v>
       </c>
     </row>
-    <row r="33" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="33" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
         <v>32</v>
       </c>
@@ -1348,7 +1455,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="34" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="34" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
         <v>33</v>
       </c>
@@ -1356,7 +1463,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="35" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="35" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
         <v>34</v>
       </c>
@@ -1364,7 +1471,7 @@
         <v>148</v>
       </c>
     </row>
-    <row r="36" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="36" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
         <v>35</v>
       </c>
@@ -1372,7 +1479,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="37" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="37" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
         <v>36</v>
       </c>
@@ -1380,7 +1487,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="38" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="38" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
         <v>37</v>
       </c>
@@ -1388,7 +1495,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="39" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="39" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
         <v>38</v>
       </c>
@@ -1396,7 +1503,7 @@
         <v>148</v>
       </c>
     </row>
-    <row r="40" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="40" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
         <v>39</v>
       </c>
@@ -1404,7 +1511,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="41" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="41" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
         <v>40</v>
       </c>
@@ -1412,7 +1519,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="42" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="42" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
         <v>41</v>
       </c>
@@ -1420,7 +1527,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="43" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="43" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
         <v>42</v>
       </c>
@@ -1428,7 +1535,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="44" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="44" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
         <v>43</v>
       </c>
@@ -1436,7 +1543,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="45" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="45" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
         <v>44</v>
       </c>
@@ -1444,7 +1551,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="46" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="46" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
         <v>45</v>
       </c>
@@ -1452,7 +1559,7 @@
         <v>148</v>
       </c>
     </row>
-    <row r="47" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="47" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
         <v>46</v>
       </c>
@@ -1460,7 +1567,7 @@
         <v>148</v>
       </c>
     </row>
-    <row r="48" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="48" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
         <v>47</v>
       </c>
@@ -1468,7 +1575,7 @@
         <v>148</v>
       </c>
     </row>
-    <row r="49" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="49" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
         <v>48</v>
       </c>
@@ -1476,7 +1583,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="50" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="50" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
         <v>49</v>
       </c>
@@ -1484,7 +1591,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="51" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="51" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
         <v>50</v>
       </c>
@@ -1492,7 +1599,7 @@
         <v>148</v>
       </c>
     </row>
-    <row r="52" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="52" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
         <v>51</v>
       </c>
@@ -1500,7 +1607,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="53" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="53" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
         <v>52</v>
       </c>
@@ -1508,7 +1615,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="54" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="54" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
         <v>53</v>
       </c>
@@ -1516,7 +1623,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="55" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="55" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
         <v>54</v>
       </c>
@@ -1524,7 +1631,7 @@
         <v>148</v>
       </c>
     </row>
-    <row r="56" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="56" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
         <v>55</v>
       </c>
@@ -1532,7 +1639,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="57" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="57" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
         <v>56</v>
       </c>
@@ -1540,7 +1647,7 @@
         <v>148</v>
       </c>
     </row>
-    <row r="58" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="58" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
         <v>57</v>
       </c>
@@ -1548,7 +1655,7 @@
         <v>148</v>
       </c>
     </row>
-    <row r="59" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="59" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
         <v>58</v>
       </c>
@@ -1556,7 +1663,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="60" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="60" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
         <v>59</v>
       </c>
@@ -1564,7 +1671,7 @@
         <v>148</v>
       </c>
     </row>
-    <row r="61" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="61" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
         <v>60</v>
       </c>
@@ -1572,7 +1679,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="62" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="62" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
         <v>61</v>
       </c>
@@ -1580,7 +1687,7 @@
         <v>148</v>
       </c>
     </row>
-    <row r="63" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="63" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
         <v>62</v>
       </c>
@@ -1588,7 +1695,7 @@
         <v>148</v>
       </c>
     </row>
-    <row r="64" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="64" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
         <v>63</v>
       </c>
@@ -1596,7 +1703,7 @@
         <v>148</v>
       </c>
     </row>
-    <row r="65" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="65" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A65" t="s">
         <v>64</v>
       </c>
@@ -1604,7 +1711,7 @@
         <v>148</v>
       </c>
     </row>
-    <row r="66" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="66" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A66" t="s">
         <v>65</v>
       </c>
@@ -1612,7 +1719,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="67" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="67" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A67" t="s">
         <v>66</v>
       </c>
@@ -1620,7 +1727,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="68" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="68" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A68" t="s">
         <v>67</v>
       </c>
@@ -1628,7 +1735,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="69" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="69" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A69" t="s">
         <v>68</v>
       </c>
@@ -1636,7 +1743,7 @@
         <v>148</v>
       </c>
     </row>
-    <row r="70" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="70" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A70" t="s">
         <v>69</v>
       </c>
@@ -1644,7 +1751,7 @@
         <v>148</v>
       </c>
     </row>
-    <row r="71" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="71" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A71" t="s">
         <v>70</v>
       </c>
@@ -1652,7 +1759,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="72" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="72" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A72" t="s">
         <v>71</v>
       </c>
@@ -1660,7 +1767,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="73" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="73" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A73" t="s">
         <v>72</v>
       </c>
@@ -1668,7 +1775,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="74" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="74" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A74" t="s">
         <v>73</v>
       </c>
@@ -1676,7 +1783,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="75" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="75" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A75" t="s">
         <v>74</v>
       </c>
@@ -1684,7 +1791,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="76" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="76" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A76" t="s">
         <v>75</v>
       </c>
@@ -1692,7 +1799,7 @@
         <v>148</v>
       </c>
     </row>
-    <row r="77" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="77" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A77" t="s">
         <v>76</v>
       </c>
@@ -1700,7 +1807,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="78" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="78" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A78" t="s">
         <v>77</v>
       </c>
@@ -1708,7 +1815,7 @@
         <v>148</v>
       </c>
     </row>
-    <row r="79" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="79" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A79" t="s">
         <v>78</v>
       </c>
@@ -1716,7 +1823,7 @@
         <v>148</v>
       </c>
     </row>
-    <row r="80" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="80" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A80" t="s">
         <v>79</v>
       </c>
@@ -1724,7 +1831,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="81" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="81" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A81" t="s">
         <v>80</v>
       </c>
@@ -1732,7 +1839,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="82" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="82" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A82" t="s">
         <v>81</v>
       </c>
@@ -1740,7 +1847,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="83" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="83" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A83" t="s">
         <v>82</v>
       </c>
@@ -1748,7 +1855,7 @@
         <v>148</v>
       </c>
     </row>
-    <row r="84" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="84" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A84" t="s">
         <v>83</v>
       </c>
@@ -1756,7 +1863,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="85" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="85" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A85" t="s">
         <v>84</v>
       </c>
@@ -1764,7 +1871,7 @@
         <v>148</v>
       </c>
     </row>
-    <row r="86" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="86" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A86" t="s">
         <v>85</v>
       </c>
@@ -1772,7 +1879,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="87" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="87" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A87" t="s">
         <v>86</v>
       </c>
@@ -1780,7 +1887,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="88" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="88" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A88" t="s">
         <v>87</v>
       </c>
@@ -1788,7 +1895,7 @@
         <v>148</v>
       </c>
     </row>
-    <row r="89" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="89" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A89" t="s">
         <v>88</v>
       </c>
@@ -1796,7 +1903,7 @@
         <v>148</v>
       </c>
     </row>
-    <row r="90" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="90" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A90" t="s">
         <v>89</v>
       </c>
@@ -1804,7 +1911,7 @@
         <v>148</v>
       </c>
     </row>
-    <row r="91" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="91" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A91" t="s">
         <v>90</v>
       </c>
@@ -1812,7 +1919,7 @@
         <v>148</v>
       </c>
     </row>
-    <row r="92" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="92" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A92" t="s">
         <v>91</v>
       </c>
@@ -1820,7 +1927,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="93" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="93" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A93" t="s">
         <v>92</v>
       </c>
@@ -1828,7 +1935,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="94" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="94" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A94" t="s">
         <v>93</v>
       </c>
@@ -1836,7 +1943,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="95" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="95" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A95" t="s">
         <v>94</v>
       </c>
@@ -1844,7 +1951,7 @@
         <v>148</v>
       </c>
     </row>
-    <row r="96" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="96" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A96" t="s">
         <v>95</v>
       </c>
@@ -1852,7 +1959,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="97" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="97" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A97" t="s">
         <v>96</v>
       </c>
@@ -1860,7 +1967,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="98" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="98" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A98" t="s">
         <v>97</v>
       </c>
@@ -1868,7 +1975,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="99" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="99" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A99" t="s">
         <v>98</v>
       </c>
@@ -1876,7 +1983,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="100" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="100" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A100" t="s">
         <v>99</v>
       </c>
@@ -1884,7 +1991,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="101" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="101" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A101" t="s">
         <v>100</v>
       </c>
@@ -1892,7 +1999,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="102" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="102" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A102" t="s">
         <v>101</v>
       </c>
@@ -1900,7 +2007,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="103" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="103" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A103" t="s">
         <v>102</v>
       </c>
@@ -1908,7 +2015,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="104" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="104" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A104" t="s">
         <v>103</v>
       </c>
@@ -1916,7 +2023,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="105" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="105" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A105" t="s">
         <v>104</v>
       </c>
@@ -1924,7 +2031,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="106" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="106" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A106" t="s">
         <v>105</v>
       </c>
@@ -1932,7 +2039,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="107" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="107" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A107" t="s">
         <v>106</v>
       </c>
@@ -1940,7 +2047,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="108" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="108" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A108" t="s">
         <v>107</v>
       </c>
@@ -1948,7 +2055,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="109" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="109" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A109" t="s">
         <v>108</v>
       </c>
@@ -1956,7 +2063,7 @@
         <v>148</v>
       </c>
     </row>
-    <row r="110" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="110" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A110" t="s">
         <v>109</v>
       </c>
@@ -1964,7 +2071,7 @@
         <v>148</v>
       </c>
     </row>
-    <row r="111" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="111" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A111" t="s">
         <v>110</v>
       </c>
@@ -1972,7 +2079,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="112" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="112" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A112" t="s">
         <v>111</v>
       </c>
@@ -1980,7 +2087,7 @@
         <v>148</v>
       </c>
     </row>
-    <row r="113" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="113" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A113" t="s">
         <v>112</v>
       </c>
@@ -1988,7 +2095,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="114" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="114" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A114" t="s">
         <v>113</v>
       </c>
@@ -1996,7 +2103,7 @@
         <v>148</v>
       </c>
     </row>
-    <row r="115" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="115" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A115" t="s">
         <v>114</v>
       </c>
@@ -2004,7 +2111,7 @@
         <v>148</v>
       </c>
     </row>
-    <row r="116" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="116" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A116" t="s">
         <v>115</v>
       </c>
@@ -2012,7 +2119,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="117" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="117" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A117" t="s">
         <v>116</v>
       </c>
@@ -2020,7 +2127,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="118" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="118" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A118" t="s">
         <v>117</v>
       </c>
@@ -2028,7 +2135,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="119" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="119" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A119" t="s">
         <v>118</v>
       </c>
@@ -2036,7 +2143,7 @@
         <v>148</v>
       </c>
     </row>
-    <row r="120" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="120" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A120" t="s">
         <v>119</v>
       </c>
@@ -2044,7 +2151,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="121" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="121" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A121" t="s">
         <v>120</v>
       </c>
@@ -2052,7 +2159,7 @@
         <v>148</v>
       </c>
     </row>
-    <row r="122" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="122" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A122" t="s">
         <v>121</v>
       </c>
@@ -2060,7 +2167,7 @@
         <v>148</v>
       </c>
     </row>
-    <row r="123" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="123" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A123" t="s">
         <v>122</v>
       </c>
@@ -2068,7 +2175,7 @@
         <v>148</v>
       </c>
     </row>
-    <row r="124" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="124" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A124" t="s">
         <v>123</v>
       </c>
@@ -2076,7 +2183,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="125" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="125" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A125" t="s">
         <v>124</v>
       </c>
@@ -2084,7 +2191,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="126" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="126" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A126" t="s">
         <v>125</v>
       </c>
@@ -2092,7 +2199,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="127" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="127" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A127" t="s">
         <v>126</v>
       </c>
@@ -2100,7 +2207,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="128" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="128" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A128" t="s">
         <v>127</v>
       </c>
@@ -2108,7 +2215,7 @@
         <v>148</v>
       </c>
     </row>
-    <row r="129" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="129" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A129" t="s">
         <v>128</v>
       </c>
@@ -2116,7 +2223,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="130" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="130" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A130" t="s">
         <v>129</v>
       </c>
@@ -2124,7 +2231,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="131" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="131" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A131" t="s">
         <v>130</v>
       </c>
@@ -2132,7 +2239,7 @@
         <v>148</v>
       </c>
     </row>
-    <row r="132" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="132" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A132" t="s">
         <v>131</v>
       </c>
@@ -2140,7 +2247,7 @@
         <v>148</v>
       </c>
     </row>
-    <row r="133" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="133" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A133" t="s">
         <v>132</v>
       </c>
@@ -2148,7 +2255,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="134" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="134" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A134" t="s">
         <v>133</v>
       </c>
@@ -2156,7 +2263,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="135" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="135" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A135" t="s">
         <v>134</v>
       </c>
@@ -2164,7 +2271,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="136" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="136" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A136" t="s">
         <v>135</v>
       </c>
@@ -2172,7 +2279,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="137" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="137" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A137" t="s">
         <v>136</v>
       </c>
@@ -2180,7 +2287,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="138" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="138" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A138" t="s">
         <v>137</v>
       </c>
@@ -2188,7 +2295,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="139" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="139" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A139" t="s">
         <v>138</v>
       </c>
@@ -2196,7 +2303,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="140" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="140" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A140" t="s">
         <v>139</v>
       </c>
@@ -2204,7 +2311,7 @@
         <v>148</v>
       </c>
     </row>
-    <row r="141" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="141" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A141" t="s">
         <v>140</v>
       </c>
@@ -2212,7 +2319,7 @@
         <v>148</v>
       </c>
     </row>
-    <row r="142" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="142" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A142" t="s">
         <v>141</v>
       </c>
@@ -2220,7 +2327,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="143" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="143" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A143" t="s">
         <v>142</v>
       </c>
@@ -2228,7 +2335,7 @@
         <v>148</v>
       </c>
     </row>
-    <row r="144" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="144" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A144" t="s">
         <v>143</v>
       </c>
@@ -2236,7 +2343,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="145" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="145" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A145" t="s">
         <v>144</v>
       </c>
@@ -2244,7 +2351,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="146" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="146" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A146" t="s">
         <v>145</v>
       </c>
@@ -2252,7 +2359,7 @@
         <v>148</v>
       </c>
     </row>
-    <row r="147" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="147" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A147" t="s">
         <v>146</v>
       </c>
